--- a/Data_Analytics/intro-to-excel.xlsx
+++ b/Data_Analytics/intro-to-excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OTAS\Desktop\Data_Science\Data_Analytics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF6A3EF3-085B-48B3-B087-122B9A10F572}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{510048DE-55FE-4752-8BA0-B4C78756D7C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{74CFDAD7-0BE6-41C8-B341-1293C24CBEED}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="20">
   <si>
     <t>Skill</t>
   </si>
@@ -72,16 +72,48 @@
   </si>
   <si>
     <t>Difficulty 1-10</t>
+  </si>
+  <si>
+    <t>b</t>
+  </si>
+  <si>
+    <t>Column1</t>
+  </si>
+  <si>
+    <t>Column2</t>
+  </si>
+  <si>
+    <t>beginner</t>
+  </si>
+  <si>
+    <t>Advanced</t>
+  </si>
+  <si>
+    <t>intermediate</t>
+  </si>
+  <si>
+    <t>Noob</t>
+  </si>
+  <si>
+    <t>Pro</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -95,15 +127,27 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -111,13 +155,70 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -482,9 +583,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A18384C8-20D0-47E7-B04F-3099B9E6FFDE}">
-  <dimension ref="C5:I10"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="2" max="3" width="10.33203125" customWidth="1"/>
     <col min="4" max="4" width="15.6640625" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="11.33203125" customWidth="1"/>
@@ -492,7 +594,51 @@
     <col min="9" max="9" width="10.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1">
+        <v>1</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>2</v>
+      </c>
+      <c r="B2" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="C2" s="7"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>3</v>
+      </c>
+      <c r="B3" s="8"/>
+      <c r="C3" s="9"/>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>4</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C5" s="1" t="s">
         <v>0</v>
       </c>
@@ -515,32 +661,135 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C6" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6" t="b">
+        <v>1</v>
+      </c>
+      <c r="F6" s="10">
+        <v>44600</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I6">
+        <f>D6*2</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C7" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="8" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7" t="b">
+        <v>1</v>
+      </c>
+      <c r="F7" s="10">
+        <v>44966</v>
+      </c>
+      <c r="G7">
+        <v>3</v>
+      </c>
+      <c r="H7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I7">
+        <f t="shared" ref="I7:I10" si="0">D7*2</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C8" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="D8">
+        <v>3</v>
+      </c>
+      <c r="E8" t="b">
+        <v>0</v>
+      </c>
+      <c r="F8" s="10">
+        <v>46003</v>
+      </c>
+      <c r="G8">
+        <v>5</v>
+      </c>
+      <c r="H8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I8">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C9" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="D9">
+        <v>4</v>
+      </c>
+      <c r="E9" t="b">
+        <v>1</v>
+      </c>
+      <c r="F9" s="10">
+        <v>46146</v>
+      </c>
+      <c r="G9">
+        <v>7</v>
+      </c>
+      <c r="H9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I9">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C10" t="s">
         <v>5</v>
       </c>
+      <c r="D10">
+        <v>5</v>
+      </c>
+      <c r="E10" t="b">
+        <v>0</v>
+      </c>
+      <c r="F10" s="10">
+        <v>46207</v>
+      </c>
+      <c r="G10">
+        <v>9</v>
+      </c>
+      <c r="H10" t="s">
+        <v>19</v>
+      </c>
+      <c r="I10">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2" xr:uid="{A892D257-3CB8-416C-951F-F1760B6007FC}">
+      <formula1>$F$2</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1:C4" xr:uid="{34EFA63B-D0CA-4DBF-B1A3-3B6C4A82EFF8}">
+      <formula1>$E$5:$E$10</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Data_Analytics/intro-to-excel.xlsx
+++ b/Data_Analytics/intro-to-excel.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OTAS\Desktop\Data_Science\Data_Analytics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{510048DE-55FE-4752-8BA0-B4C78756D7C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA92CCA5-3682-4677-93AF-15A54EB0C91E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{74CFDAD7-0BE6-41C8-B341-1293C24CBEED}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="introduction" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,8 +35,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
   <si>
     <t>Skill</t>
   </si>
@@ -65,15 +87,9 @@
     <t>DateStarted</t>
   </si>
   <si>
-    <t>level</t>
-  </si>
-  <si>
     <t>Skill &amp; level</t>
   </si>
   <si>
-    <t>Difficulty 1-10</t>
-  </si>
-  <si>
     <t>b</t>
   </si>
   <si>
@@ -96,6 +112,21 @@
   </si>
   <si>
     <t>Pro</t>
+  </si>
+  <si>
+    <t>Difficulty level</t>
+  </si>
+  <si>
+    <t>Rate</t>
+  </si>
+  <si>
+    <t>Skill_Rate</t>
+  </si>
+  <si>
+    <t>Skill_Difficulty</t>
+  </si>
+  <si>
+    <t>copy using range</t>
   </si>
 </sst>
 </file>
@@ -583,7 +614,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A18384C8-20D0-47E7-B04F-3099B9E6FFDE}">
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:V10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="3" width="10.33203125" customWidth="1"/>
@@ -592,20 +623,21 @@
     <col min="6" max="6" width="11.33203125" customWidth="1"/>
     <col min="8" max="8" width="12.77734375" customWidth="1"/>
     <col min="9" max="9" width="10.77734375" customWidth="1"/>
+    <col min="11" max="11" width="18.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A1">
         <v>1</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>2</v>
       </c>
@@ -614,31 +646,28 @@
       </c>
       <c r="C2" s="7"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>3</v>
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="9"/>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" t="s">
-        <v>12</v>
-      </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>4</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
+      </c>
+      <c r="O4" t="s">
+        <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
       <c r="C5" s="1" t="s">
         <v>0</v>
       </c>
@@ -652,16 +681,50 @@
         <v>8</v>
       </c>
       <c r="G5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>10</v>
+      <c r="J5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N5" t="str" cm="1">
+        <f t="array" ref="N5:V10">C5:K10</f>
+        <v>Skill</v>
+      </c>
+      <c r="O5" t="str">
+        <v>Difficulty 1-5</v>
+      </c>
+      <c r="P5" t="str">
+        <v>Skill known</v>
+      </c>
+      <c r="Q5" t="str">
+        <v>DateStarted</v>
+      </c>
+      <c r="R5" t="str">
+        <v>Rate</v>
+      </c>
+      <c r="S5" t="str">
+        <v>Difficulty level</v>
+      </c>
+      <c r="T5" t="str">
+        <v>Skill &amp; level</v>
+      </c>
+      <c r="U5" t="str">
+        <v>Skill_Rate</v>
+      </c>
+      <c r="V5" t="str">
+        <v>Skill_Difficulty</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="C6" t="s">
         <v>1</v>
       </c>
@@ -678,14 +741,49 @@
         <v>1</v>
       </c>
       <c r="H6" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I6">
         <f>D6*2</f>
         <v>2</v>
       </c>
+      <c r="J6" t="str">
+        <f>C6&amp;G6</f>
+        <v>Python1</v>
+      </c>
+      <c r="K6" t="str">
+        <f>C6&amp;H6</f>
+        <v>Pythonbeginner</v>
+      </c>
+      <c r="N6" t="str">
+        <v>Python</v>
+      </c>
+      <c r="O6">
+        <v>1</v>
+      </c>
+      <c r="P6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q6">
+        <v>44600</v>
+      </c>
+      <c r="R6">
+        <v>1</v>
+      </c>
+      <c r="S6" t="str">
+        <v>beginner</v>
+      </c>
+      <c r="T6">
+        <v>2</v>
+      </c>
+      <c r="U6" t="str">
+        <v>Python1</v>
+      </c>
+      <c r="V6" t="str">
+        <v>Pythonbeginner</v>
+      </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="C7" t="s">
         <v>2</v>
       </c>
@@ -702,14 +800,49 @@
         <v>3</v>
       </c>
       <c r="H7" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I7">
         <f t="shared" ref="I7:I10" si="0">D7*2</f>
         <v>4</v>
       </c>
+      <c r="J7" t="str">
+        <f t="shared" ref="J7:J10" si="1">C7&amp;G7</f>
+        <v>SQL3</v>
+      </c>
+      <c r="K7" t="str">
+        <f t="shared" ref="K7:K10" si="2">C7&amp;H7</f>
+        <v>SQLAdvanced</v>
+      </c>
+      <c r="N7" t="str">
+        <v>SQL</v>
+      </c>
+      <c r="O7">
+        <v>2</v>
+      </c>
+      <c r="P7" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q7">
+        <v>44966</v>
+      </c>
+      <c r="R7">
+        <v>3</v>
+      </c>
+      <c r="S7" t="str">
+        <v>Advanced</v>
+      </c>
+      <c r="T7">
+        <v>4</v>
+      </c>
+      <c r="U7" t="str">
+        <v>SQL3</v>
+      </c>
+      <c r="V7" t="str">
+        <v>SQLAdvanced</v>
+      </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
       <c r="C8" t="s">
         <v>3</v>
       </c>
@@ -726,14 +859,49 @@
         <v>5</v>
       </c>
       <c r="H8" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I8">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
+      <c r="J8" t="str">
+        <f t="shared" si="1"/>
+        <v>Tableau5</v>
+      </c>
+      <c r="K8" t="str">
+        <f t="shared" si="2"/>
+        <v>TableauNoob</v>
+      </c>
+      <c r="N8" t="str">
+        <v>Tableau</v>
+      </c>
+      <c r="O8">
+        <v>3</v>
+      </c>
+      <c r="P8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>46003</v>
+      </c>
+      <c r="R8">
+        <v>5</v>
+      </c>
+      <c r="S8" t="str">
+        <v>Noob</v>
+      </c>
+      <c r="T8">
+        <v>6</v>
+      </c>
+      <c r="U8" t="str">
+        <v>Tableau5</v>
+      </c>
+      <c r="V8" t="str">
+        <v>TableauNoob</v>
+      </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
       <c r="C9" t="s">
         <v>4</v>
       </c>
@@ -750,14 +918,49 @@
         <v>7</v>
       </c>
       <c r="H9" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I9">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
+      <c r="J9" t="str">
+        <f t="shared" si="1"/>
+        <v>PowerBI7</v>
+      </c>
+      <c r="K9" t="str">
+        <f t="shared" si="2"/>
+        <v>PowerBIintermediate</v>
+      </c>
+      <c r="N9" t="str">
+        <v>PowerBI</v>
+      </c>
+      <c r="O9">
+        <v>4</v>
+      </c>
+      <c r="P9" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q9">
+        <v>46146</v>
+      </c>
+      <c r="R9">
+        <v>7</v>
+      </c>
+      <c r="S9" t="str">
+        <v>intermediate</v>
+      </c>
+      <c r="T9">
+        <v>8</v>
+      </c>
+      <c r="U9" t="str">
+        <v>PowerBI7</v>
+      </c>
+      <c r="V9" t="str">
+        <v>PowerBIintermediate</v>
+      </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
       <c r="C10" t="s">
         <v>5</v>
       </c>
@@ -774,11 +977,46 @@
         <v>9</v>
       </c>
       <c r="H10" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I10">
         <f t="shared" si="0"/>
         <v>10</v>
+      </c>
+      <c r="J10" t="str">
+        <f t="shared" si="1"/>
+        <v>Excel9</v>
+      </c>
+      <c r="K10" t="str">
+        <f t="shared" si="2"/>
+        <v>ExcelPro</v>
+      </c>
+      <c r="N10" t="str">
+        <v>Excel</v>
+      </c>
+      <c r="O10">
+        <v>5</v>
+      </c>
+      <c r="P10" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q10">
+        <v>46207</v>
+      </c>
+      <c r="R10">
+        <v>9</v>
+      </c>
+      <c r="S10" t="str">
+        <v>Pro</v>
+      </c>
+      <c r="T10">
+        <v>10</v>
+      </c>
+      <c r="U10" t="str">
+        <v>Excel9</v>
+      </c>
+      <c r="V10" t="str">
+        <v>ExcelPro</v>
       </c>
     </row>
   </sheetData>

--- a/Data_Analytics/intro-to-excel.xlsx
+++ b/Data_Analytics/intro-to-excel.xlsx
@@ -8,14 +8,26 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OTAS\Desktop\Data_Science\Data_Analytics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA92CCA5-3682-4677-93AF-15A54EB0C91E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F553D01-5D50-4FDF-9AAA-07CF3F4D962D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{74CFDAD7-0BE6-41C8-B341-1293C24CBEED}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{74CFDAD7-0BE6-41C8-B341-1293C24CBEED}"/>
   </bookViews>
   <sheets>
     <sheet name="introduction" sheetId="1" r:id="rId1"/>
+    <sheet name="Graph_for_table" sheetId="3" r:id="rId2"/>
+    <sheet name="Hack" sheetId="2" r:id="rId3"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId4"/>
+  </externalReferences>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Hack!$M$36:$P$41</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
+  <pivotCaches>
+    <pivotCache cacheId="22" r:id="rId5"/>
+    <pivotCache cacheId="63" r:id="rId6"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,8 +49,9 @@
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
 <metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
+  <metadataTypes count="2">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
   <futureMetadata name="XLDAPR" count="1">
     <bk>
@@ -49,16 +62,30 @@
       </extLst>
     </bk>
   </futureMetadata>
+  <futureMetadata name="XLRICHVALUE" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
   <cellMetadata count="1">
     <bk>
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
+  <valueMetadata count="1">
+    <bk>
+      <rc t="2" v="0"/>
+    </bk>
+  </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="107">
   <si>
     <t>Skill</t>
   </si>
@@ -127,13 +154,287 @@
   </si>
   <si>
     <t>copy using range</t>
+  </si>
+  <si>
+    <t>10steps to getting you up and running with Excel</t>
+  </si>
+  <si>
+    <t>using Alt and = to sum.</t>
+  </si>
+  <si>
+    <t>1.Add</t>
+  </si>
+  <si>
+    <t>using formula to sum</t>
+  </si>
+  <si>
+    <t>Conditional additions</t>
+  </si>
+  <si>
+    <t>sum_greater_than</t>
+  </si>
+  <si>
+    <t>sum_less_than</t>
+  </si>
+  <si>
+    <t>NB: other operators are  &gt;=, &lt;=, &lt;&gt;.</t>
+  </si>
+  <si>
+    <t>2. Filling.</t>
+  </si>
+  <si>
+    <t>Banana</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="20"/>
+        <color theme="3" tint="0.89999084444715716"/>
+        <rFont val="Arial Black"/>
+        <family val="2"/>
+      </rPr>
+      <t>3.Data Stufffed - lets split it</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Flash Fill - Ctrl + E</t>
+  </si>
+  <si>
+    <t>4.TRANSPOSE</t>
+  </si>
+  <si>
+    <t>Bread</t>
+  </si>
+  <si>
+    <t>Donuts</t>
+  </si>
+  <si>
+    <t>Cookies</t>
+  </si>
+  <si>
+    <t>Cakes</t>
+  </si>
+  <si>
+    <t>Pies</t>
+  </si>
+  <si>
+    <t>Transpose - copy &amp;Paste method</t>
+  </si>
+  <si>
+    <t>butts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transpose - Formula Way </t>
+  </si>
+  <si>
+    <t>5.Sorting and Filtering</t>
+  </si>
+  <si>
+    <t>6.Tables</t>
+  </si>
+  <si>
+    <t>Column3</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>school</t>
+  </si>
+  <si>
+    <t>sex</t>
+  </si>
+  <si>
+    <t>kojo</t>
+  </si>
+  <si>
+    <t>kofi</t>
+  </si>
+  <si>
+    <t>ama</t>
+  </si>
+  <si>
+    <t>densu</t>
+  </si>
+  <si>
+    <t>araba</t>
+  </si>
+  <si>
+    <t>moh</t>
+  </si>
+  <si>
+    <t>arakan</t>
+  </si>
+  <si>
+    <t>garrison</t>
+  </si>
+  <si>
+    <t>5bm</t>
+  </si>
+  <si>
+    <t>st.marys</t>
+  </si>
+  <si>
+    <t>m</t>
+  </si>
+  <si>
+    <t>f</t>
+  </si>
+  <si>
+    <t>Naa</t>
+  </si>
+  <si>
+    <t>total</t>
+  </si>
+  <si>
+    <t>sum</t>
+  </si>
+  <si>
+    <t>7.Dropdown</t>
+  </si>
+  <si>
+    <t>Produce</t>
+  </si>
+  <si>
+    <t>Food</t>
+  </si>
+  <si>
+    <t>Dept</t>
+  </si>
+  <si>
+    <t>Apples</t>
+  </si>
+  <si>
+    <t>Beef</t>
+  </si>
+  <si>
+    <t>Lemons</t>
+  </si>
+  <si>
+    <t>Brocoli</t>
+  </si>
+  <si>
+    <t>Ham</t>
+  </si>
+  <si>
+    <t>Kale</t>
+  </si>
+  <si>
+    <t>Chicken</t>
+  </si>
+  <si>
+    <t>Bakery</t>
+  </si>
+  <si>
+    <t>Bananas</t>
+  </si>
+  <si>
+    <t>Broccoli</t>
+  </si>
+  <si>
+    <t>Department</t>
+  </si>
+  <si>
+    <t>Meat</t>
+  </si>
+  <si>
+    <t>Cereal</t>
+  </si>
+  <si>
+    <t>Vegetable</t>
+  </si>
+  <si>
+    <t>Fruits</t>
+  </si>
+  <si>
+    <t>8.Data Analysis</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Oct</t>
+  </si>
+  <si>
+    <t>Nov</t>
+  </si>
+  <si>
+    <t>Dec</t>
+  </si>
+  <si>
+    <t>Veggies</t>
+  </si>
+  <si>
+    <t>Fruit</t>
+  </si>
+  <si>
+    <t>Breads</t>
+  </si>
+  <si>
+    <t>Desserts</t>
+  </si>
+  <si>
+    <t>Deli</t>
+  </si>
+  <si>
+    <t>Sandwich</t>
+  </si>
+  <si>
+    <t>Salads</t>
+  </si>
+  <si>
+    <t>(blank)</t>
+  </si>
+  <si>
+    <t>Sum of Dec</t>
+  </si>
+  <si>
+    <t>9. Charts</t>
+  </si>
+  <si>
+    <t>10. Pivot Tables</t>
+  </si>
+  <si>
+    <t>Row Labels</t>
+  </si>
+  <si>
+    <t>Beer</t>
+  </si>
+  <si>
+    <t>Soda</t>
+  </si>
+  <si>
+    <t>Wine</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>Sum of 1400</t>
+  </si>
+  <si>
+    <t>Sum of 45982</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="3" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="44" formatCode="_-&quot;GH₵&quot;* #,##0.00_-;\-&quot;GH₵&quot;* #,##0.00_-;_-&quot;GH₵&quot;* &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -157,8 +458,106 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="Bahnschrift"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color rgb="FFFFC000"/>
+      <name val="Bahnschrift"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Arial Black"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="Arial Black"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color theme="3" tint="0.89999084444715716"/>
+      <name val="Arial Black"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="8" tint="-0.249977111117893"/>
+      <name val="Bahnschrift"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="8" tint="-0.249977111117893"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color theme="7" tint="-0.249977111117893"/>
+      <name val="Arial Black"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="20"/>
+      <color theme="8" tint="-0.249977111117893"/>
+      <name val="Arial Black"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color theme="6" tint="0.59999389629810485"/>
+      <name val="Arial Black"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFFFF00"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color rgb="FFFFFF00"/>
+      <name val="Arial Black"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="22">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -177,8 +576,116 @@
         <bgColor theme="4" tint="0.79998168889431442"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -234,28 +741,150 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="2"/>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" xfId="3"/>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="4">
+    <cellStyle name="Currency" xfId="1" builtinId="4"/>
+    <cellStyle name="GrayCell" xfId="3" xr:uid="{67A40403-B26D-4F46-8E20-5C9D48474186}"/>
+    <cellStyle name="Heading 3" xfId="2" builtinId="18"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+  <dxfs count="3">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF339966"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
+  <tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="CustomTableStyle" pivot="0" count="2" xr9:uid="{2D6B012A-14C5-409A-ADA0-0A96BAEE06E4}">
+      <tableStyleElement type="headerRow" dxfId="1"/>
+      <tableStyleElement type="firstRowStripe" dxfId="0"/>
+    </tableStyle>
     <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{5D4DD8FE-E48C-4204-86F5-5AAC35FA0A3A}"/>
   </tableStyles>
   <extLst>
@@ -267,6 +896,4948 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[intro-to-excel.xlsx]Graph_for_table!PivotTable13</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Sum of Dec by Category</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-GH"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-GH"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Graph_for_table!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Graph_for_table!$A$4:$A$12</c:f>
+              <c:strCache>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>Beef</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Breads</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Chicken</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Desserts</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Fruit</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Salads</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Sandwich</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Veggies</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>(blank)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Graph_for_table!$B$4:$B$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>200000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>20000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>150000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>120000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>40000</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>25000</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>20000</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>30000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-38D9-4036-95A0-6A7192B69928}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1544437056"/>
+        <c:axId val="1544437536"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1544437056"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-GH"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1544437536"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1544437536"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-GH"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1544437056"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-GH"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-GH"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Hack!$Y$51</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Conference attendance</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Hack!$X$52:$X$57</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2025</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2026</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Hack!$Y$52:$Y$57</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>800</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>900</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1200</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-AE4D-45F3-B125-C2CDBBD7DBC8}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1544498496"/>
+        <c:axId val="1544494656"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1544498496"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-GH"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1544494656"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1544494656"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-GH"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1544498496"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-GH"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-GH"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:areaChart>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Hack!$V$64</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Date</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:val>
+            <c:numRef>
+              <c:f>Hack!$V$65:$V$70</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2025</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2026</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-9F46-4399-B5B3-13569FBD4E3B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Hack!$W$64</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Conference attendance</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:val>
+            <c:numRef>
+              <c:f>Hack!$W$65:$W$70</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>800</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>900</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1200</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-9F46-4399-B5B3-13569FBD4E3B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1544465376"/>
+        <c:axId val="1544471616"/>
+      </c:areaChart>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Hack!$X$64</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Food sales</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>Hack!$X$65:$X$70</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>5000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>11200</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>30000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>25000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5000</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>8000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-9F46-4399-B5B3-13569FBD4E3B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1544459136"/>
+        <c:axId val="1544463936"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1544465376"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-GH"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1544471616"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1544471616"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-GH"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1544465376"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1544463936"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="r"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-GH"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1544459136"/>
+        <c:crosses val="max"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:catAx>
+        <c:axId val="1544459136"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1544463936"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-GH"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-GH"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>541020</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>11430</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>236220</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>11430</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E17E0611-65A9-4BE2-60D4-363CE7249559}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>495300</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>118110</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>118110</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{520D3894-68FC-2187-81B8-9320D1F26D16}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>53340</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>163830</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>434340</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>179070</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A96639F4-DE11-BB66-313E-B002C47E8EBF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="Start"/>
+      <sheetName val="1. Add"/>
+      <sheetName val="2. Fill"/>
+      <sheetName val="3. Split"/>
+      <sheetName val="4. Transpose"/>
+      <sheetName val="5. Sort &amp; filter"/>
+      <sheetName val="6. Tables"/>
+      <sheetName val="7. Drop-downs"/>
+      <sheetName val="8. Analyze"/>
+      <sheetName val="9. Charts"/>
+      <sheetName val="10. PivotTables"/>
+      <sheetName val="Learn more"/>
+    </sheetNames>
+    <definedNames>
+      <definedName name="ExtraCredit" refersTo="='1. Add'!$F$10:$G$15"/>
+      <definedName name="Fruit" refersTo="='1. Add'!$C$3:$D$7"/>
+      <definedName name="Items" refersTo="='1. Add'!$C$10:$D$15"/>
+      <definedName name="Meat" refersTo="='1. Add'!$F$3:$G$7"/>
+    </definedNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="3">
+          <cell r="C3" t="str">
+            <v>Fruit</v>
+          </cell>
+          <cell r="D3" t="str">
+            <v>Amount</v>
+          </cell>
+          <cell r="F3" t="str">
+            <v>Meat</v>
+          </cell>
+          <cell r="G3" t="str">
+            <v>Amount</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="C4" t="str">
+            <v>Apples</v>
+          </cell>
+          <cell r="D4">
+            <v>50</v>
+          </cell>
+          <cell r="F4" t="str">
+            <v>Beef</v>
+          </cell>
+          <cell r="G4">
+            <v>50</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="C5" t="str">
+            <v>Oranges</v>
+          </cell>
+          <cell r="D5">
+            <v>20</v>
+          </cell>
+          <cell r="F5" t="str">
+            <v>Chicken</v>
+          </cell>
+          <cell r="G5">
+            <v>30</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="C6" t="str">
+            <v>Bananas</v>
+          </cell>
+          <cell r="D6">
+            <v>60</v>
+          </cell>
+          <cell r="F6" t="str">
+            <v>Pork</v>
+          </cell>
+          <cell r="G6">
+            <v>10</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="C7" t="str">
+            <v>Lemons</v>
+          </cell>
+          <cell r="D7">
+            <v>40</v>
+          </cell>
+          <cell r="F7" t="str">
+            <v>Fish</v>
+          </cell>
+          <cell r="G7">
+            <v>50</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="C10" t="str">
+            <v>Item</v>
+          </cell>
+          <cell r="D10" t="str">
+            <v>Amount</v>
+          </cell>
+          <cell r="F10" t="str">
+            <v>Item</v>
+          </cell>
+          <cell r="G10" t="str">
+            <v>Amount</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="C11" t="str">
+            <v>Bread</v>
+          </cell>
+          <cell r="D11">
+            <v>50</v>
+          </cell>
+          <cell r="F11" t="str">
+            <v>Bread</v>
+          </cell>
+          <cell r="G11">
+            <v>50</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="C12" t="str">
+            <v>Donuts</v>
+          </cell>
+          <cell r="D12">
+            <v>100</v>
+          </cell>
+          <cell r="F12" t="str">
+            <v>Donuts</v>
+          </cell>
+          <cell r="G12">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="C13" t="str">
+            <v>Cookies</v>
+          </cell>
+          <cell r="D13">
+            <v>40</v>
+          </cell>
+          <cell r="F13" t="str">
+            <v>Cookies</v>
+          </cell>
+          <cell r="G13">
+            <v>40</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="C14" t="str">
+            <v>Cakes</v>
+          </cell>
+          <cell r="D14">
+            <v>50</v>
+          </cell>
+          <cell r="F14" t="str">
+            <v>Cakes</v>
+          </cell>
+          <cell r="G14">
+            <v>50</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="C15" t="str">
+            <v>Pies</v>
+          </cell>
+          <cell r="D15">
+            <v>20</v>
+          </cell>
+          <cell r="F15" t="str">
+            <v>Pies</v>
+          </cell>
+          <cell r="G15">
+            <v>20</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2">
+        <row r="3">
+          <cell r="C3" t="str">
+            <v>This:</v>
+          </cell>
+          <cell r="D3" t="str">
+            <v>Plus this:</v>
+          </cell>
+          <cell r="E3" t="str">
+            <v>Equals:</v>
+          </cell>
+          <cell r="F3" t="str">
+            <v>Plus this:</v>
+          </cell>
+          <cell r="G3" t="str">
+            <v>Equals:</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="C4">
+            <v>50</v>
+          </cell>
+          <cell r="D4">
+            <v>50</v>
+          </cell>
+          <cell r="E4">
+            <v>100</v>
+          </cell>
+          <cell r="F4">
+            <v>75</v>
+          </cell>
+          <cell r="G4">
+            <v>175</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="C5">
+            <v>50</v>
+          </cell>
+          <cell r="D5">
+            <v>60</v>
+          </cell>
+          <cell r="E5">
+            <v>110</v>
+          </cell>
+          <cell r="F5">
+            <v>75</v>
+          </cell>
+          <cell r="G5">
+            <v>185</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="C6">
+            <v>50</v>
+          </cell>
+          <cell r="D6">
+            <v>70</v>
+          </cell>
+          <cell r="E6">
+            <v>120</v>
+          </cell>
+          <cell r="F6">
+            <v>75</v>
+          </cell>
+          <cell r="G6">
+            <v>195</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="C7">
+            <v>50</v>
+          </cell>
+          <cell r="D7">
+            <v>80</v>
+          </cell>
+          <cell r="E7">
+            <v>130</v>
+          </cell>
+          <cell r="F7">
+            <v>75</v>
+          </cell>
+          <cell r="G7">
+            <v>205</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="C10" t="str">
+            <v>This:</v>
+          </cell>
+          <cell r="D10" t="str">
+            <v>Plus this:</v>
+          </cell>
+          <cell r="E10" t="str">
+            <v>Equals:</v>
+          </cell>
+          <cell r="F10" t="str">
+            <v>Plus this:</v>
+          </cell>
+          <cell r="G10" t="str">
+            <v>Equals:</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="C11">
+            <v>50</v>
+          </cell>
+          <cell r="D11">
+            <v>50</v>
+          </cell>
+          <cell r="E11">
+            <v>100</v>
+          </cell>
+          <cell r="F11">
+            <v>75</v>
+          </cell>
+          <cell r="G11">
+            <v>175</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="C12">
+            <v>50</v>
+          </cell>
+          <cell r="D12">
+            <v>60</v>
+          </cell>
+          <cell r="E12">
+            <v>110</v>
+          </cell>
+          <cell r="F12">
+            <v>75</v>
+          </cell>
+          <cell r="G12">
+            <v>185</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="C13">
+            <v>50</v>
+          </cell>
+          <cell r="D13">
+            <v>70</v>
+          </cell>
+          <cell r="E13">
+            <v>120</v>
+          </cell>
+          <cell r="F13">
+            <v>75</v>
+          </cell>
+          <cell r="G13">
+            <v>195</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="C14">
+            <v>50</v>
+          </cell>
+          <cell r="D14">
+            <v>80</v>
+          </cell>
+          <cell r="E14">
+            <v>130</v>
+          </cell>
+          <cell r="F14">
+            <v>75</v>
+          </cell>
+          <cell r="G14">
+            <v>205</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="C15">
+            <v>200</v>
+          </cell>
+          <cell r="D15">
+            <v>260</v>
+          </cell>
+          <cell r="E15">
+            <v>460</v>
+          </cell>
+          <cell r="F15">
+            <v>300</v>
+          </cell>
+          <cell r="G15">
+            <v>760</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="C33" t="str">
+            <v>Dept.</v>
+          </cell>
+          <cell r="D33" t="str">
+            <v>Category</v>
+          </cell>
+          <cell r="E33" t="str">
+            <v>Product</v>
+          </cell>
+          <cell r="F33" t="str">
+            <v>Count</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="C34" t="str">
+            <v>Produce</v>
+          </cell>
+          <cell r="D34" t="str">
+            <v>Fruit</v>
+          </cell>
+          <cell r="E34" t="str">
+            <v>Apple</v>
+          </cell>
+          <cell r="F34">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="C35" t="str">
+            <v>Produce</v>
+          </cell>
+          <cell r="D35" t="str">
+            <v>Fruit</v>
+          </cell>
+          <cell r="E35" t="str">
+            <v>Orange</v>
+          </cell>
+          <cell r="F35">
+            <v>200</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="C36" t="str">
+            <v>Produce</v>
+          </cell>
+          <cell r="D36" t="str">
+            <v>Fruit</v>
+          </cell>
+          <cell r="E36" t="str">
+            <v>Banana</v>
+          </cell>
+          <cell r="F36">
+            <v>50</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="C37" t="str">
+            <v>Produce</v>
+          </cell>
+          <cell r="D37" t="str">
+            <v>Fruit</v>
+          </cell>
+          <cell r="E37" t="str">
+            <v>Pears</v>
+          </cell>
+          <cell r="F37">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="47">
+          <cell r="H47" t="str">
+            <v>Qrtr 1</v>
+          </cell>
+        </row>
+        <row r="48">
+          <cell r="H48" t="str">
+            <v>Qrtr 2</v>
+          </cell>
+        </row>
+        <row r="49">
+          <cell r="H49" t="str">
+            <v>Qrtr 3</v>
+          </cell>
+        </row>
+        <row r="50">
+          <cell r="H50" t="str">
+            <v>Qrtr 4</v>
+          </cell>
+        </row>
+        <row r="60">
+          <cell r="C60" t="str">
+            <v>Intervals</v>
+          </cell>
+        </row>
+        <row r="61">
+          <cell r="C61">
+            <v>15</v>
+          </cell>
+          <cell r="D61">
+            <v>30</v>
+          </cell>
+          <cell r="E61">
+            <v>45</v>
+          </cell>
+          <cell r="F61">
+            <v>60</v>
+          </cell>
+          <cell r="G61">
+            <v>75</v>
+          </cell>
+          <cell r="H61">
+            <v>90</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3">
+        <row r="4">
+          <cell r="C4" t="str">
+            <v>Email</v>
+          </cell>
+          <cell r="D4" t="str">
+            <v>First name</v>
+          </cell>
+          <cell r="E4" t="str">
+            <v>Last name</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="C5" t="str">
+            <v>Nancy.Smith@contoso.com</v>
+          </cell>
+          <cell r="D5" t="str">
+            <v>Nancy</v>
+          </cell>
+          <cell r="E5" t="str">
+            <v>Smith</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="C6" t="str">
+            <v>Andy.North@fabrikam.com</v>
+          </cell>
+          <cell r="D6" t="str">
+            <v>Andy</v>
+          </cell>
+          <cell r="E6" t="str">
+            <v>North</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="C7" t="str">
+            <v>Jan.Kotas@relecloud.com</v>
+          </cell>
+          <cell r="D7" t="str">
+            <v>Jan</v>
+          </cell>
+          <cell r="E7" t="str">
+            <v>Kotas</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="C8" t="str">
+            <v>Mariya.Jones@contoso.com</v>
+          </cell>
+          <cell r="D8" t="str">
+            <v>Mariya</v>
+          </cell>
+          <cell r="E8" t="str">
+            <v>Jones</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="C9" t="str">
+            <v xml:space="preserve">Yvonne.McKay@fabrikam.com </v>
+          </cell>
+          <cell r="D9" t="str">
+            <v>Yvonne</v>
+          </cell>
+          <cell r="E9" t="str">
+            <v>McKay</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="C31" t="str">
+            <v>Data</v>
+          </cell>
+          <cell r="D31" t="str">
+            <v>First name</v>
+          </cell>
+          <cell r="E31" t="str">
+            <v>Last name</v>
+          </cell>
+          <cell r="F31" t="str">
+            <v>Company name</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="C32" t="str">
+            <v>Nancy,Smith,Contoso Ltd.</v>
+          </cell>
+          <cell r="D32" t="str">
+            <v>Nancy</v>
+          </cell>
+          <cell r="E32" t="str">
+            <v>Smith</v>
+          </cell>
+          <cell r="F32" t="str">
+            <v>Contoso Ltd.</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="C33" t="str">
+            <v>Andy,North,Fabrikam Inc.</v>
+          </cell>
+          <cell r="D33" t="str">
+            <v>Andy</v>
+          </cell>
+          <cell r="E33" t="str">
+            <v>North</v>
+          </cell>
+          <cell r="F33" t="str">
+            <v>Fabrikam Inc.</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="C34" t="str">
+            <v>Jan,Kotas,Relecloud</v>
+          </cell>
+          <cell r="D34" t="str">
+            <v>Jan</v>
+          </cell>
+          <cell r="E34" t="str">
+            <v>Kotas</v>
+          </cell>
+          <cell r="F34" t="str">
+            <v>Relecloud</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="C35" t="str">
+            <v>Mariya,Jones,Contoso Ltd.</v>
+          </cell>
+          <cell r="D35" t="str">
+            <v>Mariya</v>
+          </cell>
+          <cell r="E35" t="str">
+            <v>Jones</v>
+          </cell>
+          <cell r="F35" t="str">
+            <v>Contoso Ltd.</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="C36" t="str">
+            <v>Steven,Thorpe,Relecloud</v>
+          </cell>
+          <cell r="D36" t="str">
+            <v>Steven</v>
+          </cell>
+          <cell r="E36" t="str">
+            <v>Thorpe</v>
+          </cell>
+          <cell r="F36" t="str">
+            <v>Relecloud</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="C37" t="str">
+            <v>Michael,Neipper,Fabrikam Inc.</v>
+          </cell>
+          <cell r="D37" t="str">
+            <v>Michael</v>
+          </cell>
+          <cell r="E37" t="str">
+            <v>Neipper</v>
+          </cell>
+          <cell r="F37" t="str">
+            <v>Fabrikam Inc.</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="C38" t="str">
+            <v>Robert,Zare,Relecloud</v>
+          </cell>
+          <cell r="D38" t="str">
+            <v>Robert</v>
+          </cell>
+          <cell r="E38" t="str">
+            <v>Zare</v>
+          </cell>
+          <cell r="F38" t="str">
+            <v>Relecloud</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="C39" t="str">
+            <v>Yvonne,McKay,Contoso Ltd.</v>
+          </cell>
+          <cell r="D39" t="str">
+            <v>Yvonne</v>
+          </cell>
+          <cell r="E39" t="str">
+            <v>McKay</v>
+          </cell>
+          <cell r="F39" t="str">
+            <v>Contoso Ltd.</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="4">
+        <row r="5">
+          <cell r="C5" t="str">
+            <v>Item</v>
+          </cell>
+          <cell r="D5" t="str">
+            <v>Bread</v>
+          </cell>
+          <cell r="E5" t="str">
+            <v>Donuts</v>
+          </cell>
+          <cell r="F5" t="str">
+            <v>Cookies</v>
+          </cell>
+          <cell r="G5" t="str">
+            <v>Cakes</v>
+          </cell>
+          <cell r="H5" t="str">
+            <v>Pies</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="C6" t="str">
+            <v>Amount</v>
+          </cell>
+          <cell r="D6">
+            <v>50</v>
+          </cell>
+          <cell r="E6">
+            <v>100</v>
+          </cell>
+          <cell r="F6">
+            <v>40</v>
+          </cell>
+          <cell r="G6">
+            <v>50</v>
+          </cell>
+          <cell r="H6">
+            <v>20</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="C10" t="str">
+            <v>Bread</v>
+          </cell>
+          <cell r="D10">
+            <v>50</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="C11" t="str">
+            <v>Donuts</v>
+          </cell>
+          <cell r="D11">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="C12" t="str">
+            <v>Cookies</v>
+          </cell>
+          <cell r="D12">
+            <v>40</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="C13" t="str">
+            <v>Cakes</v>
+          </cell>
+          <cell r="D13">
+            <v>50</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="C14" t="str">
+            <v>Pies</v>
+          </cell>
+          <cell r="D14">
+            <v>20</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="5">
+        <row r="5">
+          <cell r="C5" t="str">
+            <v>Department</v>
+          </cell>
+          <cell r="D5" t="str">
+            <v>Category</v>
+          </cell>
+          <cell r="E5" t="str">
+            <v>Oct</v>
+          </cell>
+          <cell r="F5" t="str">
+            <v>Nov</v>
+          </cell>
+          <cell r="G5" t="str">
+            <v>Dec</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="C6" t="str">
+            <v>Meat</v>
+          </cell>
+          <cell r="D6" t="str">
+            <v>Chicken</v>
+          </cell>
+          <cell r="E6">
+            <v>75000</v>
+          </cell>
+          <cell r="F6">
+            <v>82000</v>
+          </cell>
+          <cell r="G6">
+            <v>2000000</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="C7" t="str">
+            <v>Bakery</v>
+          </cell>
+          <cell r="D7" t="str">
+            <v>Desserts</v>
+          </cell>
+          <cell r="E7">
+            <v>25000</v>
+          </cell>
+          <cell r="F7">
+            <v>80000</v>
+          </cell>
+          <cell r="G7">
+            <v>120000</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="C8" t="str">
+            <v>Meat</v>
+          </cell>
+          <cell r="D8" t="str">
+            <v>Beef</v>
+          </cell>
+          <cell r="E8">
+            <v>90000</v>
+          </cell>
+          <cell r="F8">
+            <v>110000</v>
+          </cell>
+          <cell r="G8">
+            <v>120000</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="C9" t="str">
+            <v>Produce</v>
+          </cell>
+          <cell r="D9" t="str">
+            <v>Fruit</v>
+          </cell>
+          <cell r="E9">
+            <v>10000</v>
+          </cell>
+          <cell r="F9">
+            <v>30000</v>
+          </cell>
+          <cell r="G9">
+            <v>40000</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="C10" t="str">
+            <v>Produce</v>
+          </cell>
+          <cell r="D10" t="str">
+            <v>Veggies</v>
+          </cell>
+          <cell r="E10">
+            <v>30000</v>
+          </cell>
+          <cell r="F10">
+            <v>80000</v>
+          </cell>
+          <cell r="G10">
+            <v>30000</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="C11" t="str">
+            <v>Deli</v>
+          </cell>
+          <cell r="D11" t="str">
+            <v>Salads</v>
+          </cell>
+          <cell r="E11">
+            <v>90000</v>
+          </cell>
+          <cell r="F11">
+            <v>35000</v>
+          </cell>
+          <cell r="G11">
+            <v>25000</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="C12" t="str">
+            <v>Bakery</v>
+          </cell>
+          <cell r="D12" t="str">
+            <v>Breads</v>
+          </cell>
+          <cell r="E12">
+            <v>30000</v>
+          </cell>
+          <cell r="F12">
+            <v>15000</v>
+          </cell>
+          <cell r="G12">
+            <v>20000</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="C13" t="str">
+            <v>Deli</v>
+          </cell>
+          <cell r="D13" t="str">
+            <v>Sandwiches</v>
+          </cell>
+          <cell r="E13">
+            <v>80000</v>
+          </cell>
+          <cell r="F13">
+            <v>40000</v>
+          </cell>
+          <cell r="G13">
+            <v>20000</v>
+          </cell>
+        </row>
+        <row r="49">
+          <cell r="C49" t="str">
+            <v>Expense date</v>
+          </cell>
+          <cell r="D49" t="str">
+            <v>Employee</v>
+          </cell>
+          <cell r="E49" t="str">
+            <v>Food</v>
+          </cell>
+          <cell r="F49" t="str">
+            <v>Hotel</v>
+          </cell>
+        </row>
+        <row r="50">
+          <cell r="C50">
+            <v>46037</v>
+          </cell>
+          <cell r="D50" t="str">
+            <v>Jackie</v>
+          </cell>
+          <cell r="E50">
+            <v>21</v>
+          </cell>
+          <cell r="F50">
+            <v>3820</v>
+          </cell>
+        </row>
+        <row r="51">
+          <cell r="C51">
+            <v>46036</v>
+          </cell>
+          <cell r="D51" t="str">
+            <v>Mark</v>
+          </cell>
+          <cell r="E51">
+            <v>62</v>
+          </cell>
+          <cell r="F51">
+            <v>2112</v>
+          </cell>
+        </row>
+        <row r="52">
+          <cell r="C52">
+            <v>46039</v>
+          </cell>
+          <cell r="D52" t="str">
+            <v>Tricia</v>
+          </cell>
+          <cell r="E52">
+            <v>30</v>
+          </cell>
+          <cell r="F52">
+            <v>3085</v>
+          </cell>
+        </row>
+        <row r="53">
+          <cell r="C53">
+            <v>46033</v>
+          </cell>
+          <cell r="D53" t="str">
+            <v>Dave</v>
+          </cell>
+          <cell r="E53">
+            <v>25</v>
+          </cell>
+          <cell r="F53">
+            <v>1611</v>
+          </cell>
+        </row>
+        <row r="54">
+          <cell r="C54">
+            <v>46034</v>
+          </cell>
+          <cell r="D54" t="str">
+            <v>Laura</v>
+          </cell>
+          <cell r="E54">
+            <v>45</v>
+          </cell>
+          <cell r="F54">
+            <v>5050</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="6">
+        <row r="5">
+          <cell r="C5" t="str">
+            <v>Department</v>
+          </cell>
+          <cell r="D5" t="str">
+            <v>Category</v>
+          </cell>
+          <cell r="E5" t="str">
+            <v>Oct</v>
+          </cell>
+          <cell r="F5" t="str">
+            <v>Nov</v>
+          </cell>
+          <cell r="G5" t="str">
+            <v>Dec</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="C6" t="str">
+            <v>Produce</v>
+          </cell>
+          <cell r="D6" t="str">
+            <v>Veggies</v>
+          </cell>
+          <cell r="E6">
+            <v>30000</v>
+          </cell>
+          <cell r="F6">
+            <v>80000</v>
+          </cell>
+          <cell r="G6">
+            <v>30000</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="C7" t="str">
+            <v>Produce</v>
+          </cell>
+          <cell r="D7" t="str">
+            <v>Fruit</v>
+          </cell>
+          <cell r="E7">
+            <v>10000</v>
+          </cell>
+          <cell r="F7">
+            <v>30000</v>
+          </cell>
+          <cell r="G7">
+            <v>40000</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="C8" t="str">
+            <v>Bakery</v>
+          </cell>
+          <cell r="D8" t="str">
+            <v>Breads</v>
+          </cell>
+          <cell r="E8">
+            <v>30000</v>
+          </cell>
+          <cell r="F8">
+            <v>15000</v>
+          </cell>
+          <cell r="G8">
+            <v>20000</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="C9" t="str">
+            <v>Bakery</v>
+          </cell>
+          <cell r="D9" t="str">
+            <v>Desserts</v>
+          </cell>
+          <cell r="E9">
+            <v>25000</v>
+          </cell>
+          <cell r="F9">
+            <v>80000</v>
+          </cell>
+          <cell r="G9">
+            <v>120000</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="C10" t="str">
+            <v>Deli</v>
+          </cell>
+          <cell r="D10" t="str">
+            <v>Sandwich</v>
+          </cell>
+          <cell r="E10">
+            <v>80000</v>
+          </cell>
+          <cell r="F10">
+            <v>40000</v>
+          </cell>
+          <cell r="G10">
+            <v>20000</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="C11" t="str">
+            <v>Deli</v>
+          </cell>
+          <cell r="D11" t="str">
+            <v>Salads</v>
+          </cell>
+          <cell r="E11">
+            <v>90000</v>
+          </cell>
+          <cell r="F11">
+            <v>35000</v>
+          </cell>
+          <cell r="G11">
+            <v>25000</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="C12" t="str">
+            <v>Meat</v>
+          </cell>
+          <cell r="D12" t="str">
+            <v>Beef</v>
+          </cell>
+          <cell r="E12">
+            <v>90000</v>
+          </cell>
+          <cell r="F12">
+            <v>110000</v>
+          </cell>
+          <cell r="G12">
+            <v>200000</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="C13" t="str">
+            <v>Meat</v>
+          </cell>
+          <cell r="D13" t="str">
+            <v>Chicken</v>
+          </cell>
+          <cell r="E13">
+            <v>75000</v>
+          </cell>
+          <cell r="F13">
+            <v>82000</v>
+          </cell>
+          <cell r="G13">
+            <v>150000</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="C14" t="str">
+            <v>rice</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="7">
+        <row r="3">
+          <cell r="C3" t="str">
+            <v>Food</v>
+          </cell>
+          <cell r="D3" t="str">
+            <v>Department</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="C4" t="str">
+            <v>Apples</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="C5" t="str">
+            <v>Beef</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="C6" t="str">
+            <v>Bananas</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="C7" t="str">
+            <v>Lemons</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="C8" t="str">
+            <v>Broccoli</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="C9" t="str">
+            <v>Kale</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="C10" t="str">
+            <v>Ham</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="C11" t="str">
+            <v>Bread</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="C12" t="str">
+            <v>Chicken</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="C13" t="str">
+            <v>Cookies</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="C14" t="str">
+            <v>Cakes</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="C15" t="str">
+            <v>Pies</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="8">
+        <row r="5">
+          <cell r="C5" t="str">
+            <v>Department</v>
+          </cell>
+          <cell r="D5" t="str">
+            <v>Category</v>
+          </cell>
+          <cell r="F5" t="str">
+            <v>Nov</v>
+          </cell>
+          <cell r="G5" t="str">
+            <v>Dec</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="C6" t="str">
+            <v>Produce</v>
+          </cell>
+          <cell r="D6" t="str">
+            <v>Veggies</v>
+          </cell>
+          <cell r="F6">
+            <v>80000</v>
+          </cell>
+          <cell r="G6">
+            <v>30000</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="C7" t="str">
+            <v>Produce</v>
+          </cell>
+          <cell r="D7" t="str">
+            <v>Fruit</v>
+          </cell>
+          <cell r="F7">
+            <v>30000</v>
+          </cell>
+          <cell r="G7">
+            <v>40000</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="C10" t="str">
+            <v>Deli</v>
+          </cell>
+          <cell r="D10" t="str">
+            <v>Sandwich</v>
+          </cell>
+          <cell r="F10">
+            <v>40000</v>
+          </cell>
+          <cell r="G10">
+            <v>20000</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="C11" t="str">
+            <v>Deli</v>
+          </cell>
+          <cell r="D11" t="str">
+            <v>Salads</v>
+          </cell>
+          <cell r="F11">
+            <v>35000</v>
+          </cell>
+          <cell r="G11">
+            <v>25000</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="C12" t="str">
+            <v>Meat</v>
+          </cell>
+          <cell r="D12" t="str">
+            <v>Beef</v>
+          </cell>
+          <cell r="F12">
+            <v>110000</v>
+          </cell>
+          <cell r="G12">
+            <v>200000</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="C13" t="str">
+            <v>Meat</v>
+          </cell>
+          <cell r="D13" t="str">
+            <v>Chicken</v>
+          </cell>
+          <cell r="F13">
+            <v>82000</v>
+          </cell>
+          <cell r="G13">
+            <v>150000</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="9">
+        <row r="5">
+          <cell r="C5" t="str">
+            <v>Year</v>
+          </cell>
+          <cell r="D5" t="str">
+            <v>Conference attendance</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="C6">
+            <v>2021</v>
+          </cell>
+          <cell r="D6">
+            <v>500</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="C7">
+            <v>2022</v>
+          </cell>
+          <cell r="D7">
+            <v>800</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="C10">
+            <v>2025</v>
+          </cell>
+          <cell r="D10">
+            <v>1000</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="C11">
+            <v>2026</v>
+          </cell>
+          <cell r="D11">
+            <v>1200</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="10">
+        <row r="3">
+          <cell r="C3" t="str">
+            <v>Date</v>
+          </cell>
+          <cell r="D3" t="str">
+            <v>Salesperson</v>
+          </cell>
+          <cell r="F3" t="str">
+            <v>Amount</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="C4">
+            <v>45982</v>
+          </cell>
+          <cell r="D4" t="str">
+            <v>Anne</v>
+          </cell>
+          <cell r="F4">
+            <v>1400</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="C5">
+            <v>45987</v>
+          </cell>
+          <cell r="D5" t="str">
+            <v>Mark</v>
+          </cell>
+          <cell r="F5">
+            <v>1010</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="C6">
+            <v>46004</v>
+          </cell>
+          <cell r="D6" t="str">
+            <v>Anne</v>
+          </cell>
+          <cell r="F6">
+            <v>750</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="C7">
+            <v>46008</v>
+          </cell>
+          <cell r="D7" t="str">
+            <v>Mark</v>
+          </cell>
+          <cell r="F7">
+            <v>510</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="F11" t="str">
+            <v>Sum of Amount</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="F13">
+            <v>2150</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="F14">
+            <v>2150</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="11"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OTAS" refreshedDate="46039.157231597223" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="10" xr:uid="{5A94F3B7-A217-4624-B43A-93A1695C8200}">
+  <cacheSource type="worksheet">
+    <worksheetSource name="AnalyzeData"/>
+  </cacheSource>
+  <cacheFields count="5">
+    <cacheField name="Department" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="Category" numFmtId="0">
+      <sharedItems containsBlank="1" count="9">
+        <s v="Breads"/>
+        <s v="Sandwich"/>
+        <s v="Salads"/>
+        <s v="Veggies"/>
+        <s v="Fruit"/>
+        <s v="Desserts"/>
+        <s v="Chicken"/>
+        <s v="Beef"/>
+        <m/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Oct" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="30000" maxValue="30000"/>
+    </cacheField>
+    <cacheField name="Nov" numFmtId="44">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="15000" maxValue="110000"/>
+    </cacheField>
+    <cacheField name="Dec" numFmtId="44">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="20000" maxValue="200000"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OTAS" refreshedDate="46039.217250578702" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="5" xr:uid="{5F339209-DAB5-41B0-8A8D-13C38FCFD0C4}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="V90:Y95" sheet="Hack"/>
+  </cacheSource>
+  <cacheFields count="4">
+    <cacheField name="45982" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="45987" maxValue="46039"/>
+    </cacheField>
+    <cacheField name="Anne" numFmtId="0">
+      <sharedItems count="4">
+        <s v="Mark"/>
+        <s v="Anne"/>
+        <s v="Mariya"/>
+        <s v="Laura"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Beer" numFmtId="0">
+      <sharedItems count="3">
+        <s v="Wine"/>
+        <s v="Beer"/>
+        <s v="Soda"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="1400" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="510" maxValue="1600"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+    <ext xmlns:xlpds="http://schemas.microsoft.com/office/spreadsheetml/2025/pivotDataSource" uri="{1DE1FBE3-BBE2-450B-8D17-3B53B619325D}">
+      <xlpds:pivotCacheDataSource ref="V90"/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="10">
+  <r>
+    <s v="Bakery"/>
+    <x v="0"/>
+    <n v="30000"/>
+    <n v="15000"/>
+    <n v="20000"/>
+  </r>
+  <r>
+    <s v="Deli"/>
+    <x v="1"/>
+    <n v="30000"/>
+    <n v="40000"/>
+    <n v="20000"/>
+  </r>
+  <r>
+    <s v="Deli"/>
+    <x v="2"/>
+    <n v="30000"/>
+    <n v="35000"/>
+    <n v="25000"/>
+  </r>
+  <r>
+    <s v="Produce"/>
+    <x v="3"/>
+    <n v="30000"/>
+    <n v="80000"/>
+    <n v="30000"/>
+  </r>
+  <r>
+    <s v="Produce"/>
+    <x v="4"/>
+    <n v="30000"/>
+    <n v="30000"/>
+    <n v="40000"/>
+  </r>
+  <r>
+    <s v="Bakery"/>
+    <x v="5"/>
+    <n v="30000"/>
+    <n v="80000"/>
+    <n v="120000"/>
+  </r>
+  <r>
+    <s v="Meat"/>
+    <x v="6"/>
+    <n v="30000"/>
+    <n v="82000"/>
+    <n v="150000"/>
+  </r>
+  <r>
+    <s v="Meat"/>
+    <x v="7"/>
+    <n v="30000"/>
+    <n v="110000"/>
+    <n v="200000"/>
+  </r>
+  <r>
+    <m/>
+    <x v="8"/>
+    <n v="30000"/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="8"/>
+    <n v="30000"/>
+    <m/>
+    <m/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="5">
+  <r>
+    <n v="45987"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="1010"/>
+  </r>
+  <r>
+    <n v="46004"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="750"/>
+  </r>
+  <r>
+    <n v="46008"/>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="510"/>
+  </r>
+  <r>
+    <n v="46028"/>
+    <x v="2"/>
+    <x v="2"/>
+    <n v="1600"/>
+  </r>
+  <r>
+    <n v="46039"/>
+    <x v="3"/>
+    <x v="0"/>
+    <n v="680"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{085FEC23-AF54-4C1C-94BD-9B20AB72BB94}" name="PivotTable13" cacheId="22" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="1">
+  <location ref="A3:B12" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="5">
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
+      <items count="9">
+        <item x="7"/>
+        <item x="0"/>
+        <item x="6"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="8"/>
+      </items>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField dataField="1" compact="0" outline="0" showAll="0" defaultSubtotal="0">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="9">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Dec" fld="4" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" fillDownLabelsDefault="1" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9AEEC572-0495-4002-9FB9-9DC2F045095E}" name="PivotTable31" cacheId="63" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="V96:X100" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="4">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="1"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="1"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <dataFields count="2">
+    <dataField name="Sum of 1400" fld="3" baseField="0" baseItem="0"/>
+    <dataField name="Sum of 45982" fld="0" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+    <ext xmlns:xxpvi="http://schemas.microsoft.com/office/spreadsheetml/2022/pivotVersionInfo" uri="{9F748A41-CAEA-4470-BF7A-CE61E8FFA7F9}">
+      <xxpvi:pivotVersionInfo>
+        <xxpvi:lastUpdateFeature>PivotDynamicArray</xxpvi:lastUpdateFeature>
+      </xxpvi:pivotVersionInfo>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
+<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
+  <global>
+    <keyFlags>
+      <key name="_Self">
+        <flag name="ExcludeFromFile" value="1"/>
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_DisplayString">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Flags">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Format">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_SubLabel">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Attribution">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Icon">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Display">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_CanonicalPropertyNames">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_ClassificationId">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+    </keyFlags>
+  </global>
+</rvTypesInfo>
+</file>
+
+<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <rv s="0">
+    <v>2</v>
+    <v>8</v>
+    <v>9</v>
+    <v>5</v>
+  </rv>
+</rvData>
+</file>
+
+<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <s t="_error">
+    <k n="colOffset" t="i"/>
+    <k n="errorType" t="i"/>
+    <k n="rwOffset" t="i"/>
+    <k n="subType" t="i"/>
+  </s>
+</rvStructures>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{D9B01F17-C16C-4477-8069-4B18DE004C7F}" name="Table4" displayName="Table4" ref="M74:P81" totalsRowShown="0">
+  <autoFilter ref="M74:P81" xr:uid="{D9B01F17-C16C-4477-8069-4B18DE004C7F}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{B52732CB-FC8F-42BF-8A21-C08E40537938}" name="Column1"/>
+    <tableColumn id="2" xr3:uid="{D2270CB0-DB04-4051-AC2C-7C2DAA98B6C8}" name="Column2"/>
+    <tableColumn id="3" xr3:uid="{E029EC42-2E8C-458F-AEFF-C4AA8F9B5BF7}" name="Column3"/>
+    <tableColumn id="4" xr3:uid="{D1F0772F-4737-48DF-A048-BA6C197ECF69}" name="total"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{B747798F-3680-453E-ABEC-24D241E87F2E}" name="Table5" displayName="Table5" ref="M94:O104" totalsRowShown="0">
+  <autoFilter ref="M94:O104" xr:uid="{B747798F-3680-453E-ABEC-24D241E87F2E}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{303A5E28-06B9-426B-800C-1BD220AB0898}" name="Column1"/>
+    <tableColumn id="2" xr3:uid="{7AE58B62-DD45-40BB-BBA3-EE624ACB7482}" name="Column2"/>
+    <tableColumn id="3" xr3:uid="{B8DF37CB-352C-497A-9E5C-62213F375033}" name="Column3"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{9AAC6AD7-886E-4408-9768-858CFB07FFAC}" name="Table6" displayName="Table6" ref="AC20:AC26" headerRowBorderDxfId="2" headerRowCellStyle="Heading 3">
+  <autoFilter ref="AC20:AC26" xr:uid="{9AAC6AD7-886E-4408-9768-858CFB07FFAC}"/>
+  <tableColumns count="1">
+    <tableColumn id="1" xr3:uid="{6B4999AF-0C35-4E0A-B8D1-C1A9A77C755D}" name="Department" totalsRowFunction="count"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{DAAAA327-2AD8-4368-B0A0-20F34655415C}" name="AnalyzeData" displayName="AnalyzeData" ref="V31:Z41" totalsRowShown="0">
+  <autoFilter ref="V31:Z41" xr:uid="{DAAAA327-2AD8-4368-B0A0-20F34655415C}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="V32:Z39">
+    <sortCondition ref="Z31:Z39"/>
+  </sortState>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{E1D84317-2BB6-4A19-8C6F-C6B9FFC6574E}" name="Department"/>
+    <tableColumn id="2" xr3:uid="{A04F93B2-1460-4C20-922A-081418ADEED7}" name="Category"/>
+    <tableColumn id="3" xr3:uid="{FF38654B-7A49-47E6-9206-7D7A2F9B7D2A}" name="Oct" dataCellStyle="Currency"/>
+    <tableColumn id="4" xr3:uid="{57FB9271-DA6E-4987-8BBF-E239F9DF72E0}" name="Nov" dataCellStyle="Currency"/>
+    <tableColumn id="5" xr3:uid="{CC224304-5A50-4EBF-841C-B8ECDF1D4E50}" name="Dec" dataCellStyle="Currency"/>
+  </tableColumns>
+  <tableStyleInfo name="CustomTableStyle" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{504A1905-F514-4f6f-8877-14C23A59335A}">
+      <x14:table altTextSummary="Quick Analysis table for filtering data. This sample data has Department, Category, Oct, Nov, and Dec amounts with sample data"/>
+    </ext>
+  </extLst>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -602,6 +6173,9 @@
   <we:bindings/>
   <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
   <we:extLst>
+    <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uri="{D87F86FE-615C-45B5-9D79-34F1136793EB}">
+      <we:containsCustomFunctions/>
+    </a:ext>
     <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uri="{7C84B067-C214-45C3-A712-C9D94CD141B2}">
       <we:customFunctionIdList>
         <we:customFunctionIds>_xldudf_BOARDFLARE_RUNPY</we:customFunctionIds>
@@ -1030,4 +6604,3120 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87767F41-E7A4-4E4E-BDA3-35014FD39B5B}">
+  <dimension ref="A3:B12"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.21875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="36" t="s">
+        <v>85</v>
+      </c>
+      <c r="B3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B4" s="37">
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>91</v>
+      </c>
+      <c r="B5" s="37">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>75</v>
+      </c>
+      <c r="B6" s="37">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>92</v>
+      </c>
+      <c r="B7" s="37">
+        <v>120000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>90</v>
+      </c>
+      <c r="B8" s="37">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>95</v>
+      </c>
+      <c r="B9" s="37">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>94</v>
+      </c>
+      <c r="B10" s="37">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>89</v>
+      </c>
+      <c r="B11" s="37">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>96</v>
+      </c>
+      <c r="B12" s="37"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D72B8E2B-2A1F-45B6-8C18-BFECD6D607E8}">
+  <sheetPr filterMode="1"/>
+  <dimension ref="A2:AG100"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="2" max="2" width="15.21875" customWidth="1"/>
+    <col min="3" max="3" width="14.44140625" customWidth="1"/>
+    <col min="4" max="4" width="17.21875" customWidth="1"/>
+    <col min="12" max="12" width="14.109375" customWidth="1"/>
+    <col min="13" max="13" width="13.77734375" customWidth="1"/>
+    <col min="14" max="14" width="10.5546875" customWidth="1"/>
+    <col min="15" max="15" width="10.33203125" customWidth="1"/>
+    <col min="22" max="22" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="11" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="12" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="15.21875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="12.88671875" customWidth="1"/>
+    <col min="31" max="31" width="11.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:33" s="25" customFormat="1" ht="22.2" x14ac:dyDescent="0.35">
+      <c r="A2" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
+      <c r="I2" s="24"/>
+      <c r="J2" s="24"/>
+      <c r="K2" s="24"/>
+    </row>
+    <row r="4" spans="1:33" ht="30" x14ac:dyDescent="0.7">
+      <c r="D4" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="17"/>
+      <c r="K4" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="L4" s="26"/>
+      <c r="M4" s="26"/>
+      <c r="N4" s="26"/>
+      <c r="O4" s="26"/>
+      <c r="P4" s="26"/>
+      <c r="Q4" s="26"/>
+      <c r="R4" s="26"/>
+      <c r="U4" s="30" t="s">
+        <v>65</v>
+      </c>
+      <c r="V4" s="29"/>
+      <c r="W4" s="29"/>
+      <c r="X4" s="29"/>
+      <c r="Y4" s="29"/>
+      <c r="Z4" s="29"/>
+      <c r="AA4" s="29"/>
+      <c r="AB4" s="29"/>
+      <c r="AC4" s="29"/>
+      <c r="AD4" s="29"/>
+      <c r="AE4" s="29"/>
+      <c r="AF4" s="29"/>
+      <c r="AG4" s="29"/>
+    </row>
+    <row r="5" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A5" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="11"/>
+    </row>
+    <row r="6" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" t="str" cm="1">
+        <f t="array" ref="A6:B10">[1]!Fruit</f>
+        <v>Fruit</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Amount</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+      <c r="L6" t="str" cm="1">
+        <f t="array" ref="L6:P14">'[1]5. Sort &amp; filter'!$C$5:$G$13</f>
+        <v>Department</v>
+      </c>
+      <c r="M6" t="str">
+        <v>Category</v>
+      </c>
+      <c r="N6" t="str">
+        <v>Oct</v>
+      </c>
+      <c r="O6" t="str">
+        <v>Nov</v>
+      </c>
+      <c r="P6" t="str">
+        <v>Dec</v>
+      </c>
+      <c r="W6" t="str" cm="1">
+        <f t="array" ref="W6:X18">'[1]7. Drop-downs'!$C$3:$D$15</f>
+        <v>Food</v>
+      </c>
+      <c r="X6" t="str">
+        <v>Department</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>68</v>
+      </c>
+      <c r="AD6" s="31" t="s">
+        <v>67</v>
+      </c>
+      <c r="AE6" s="31" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="7" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A7" t="str">
+        <v>Apples</v>
+      </c>
+      <c r="B7">
+        <v>50</v>
+      </c>
+      <c r="L7" t="str">
+        <v>Meat</v>
+      </c>
+      <c r="M7" t="str">
+        <v>Chicken</v>
+      </c>
+      <c r="N7">
+        <v>75000</v>
+      </c>
+      <c r="O7">
+        <v>82000</v>
+      </c>
+      <c r="P7">
+        <v>2000000</v>
+      </c>
+      <c r="W7" t="str">
+        <v>Apples</v>
+      </c>
+      <c r="X7">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD7" s="32" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="8" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A8" t="str">
+        <v>Oranges</v>
+      </c>
+      <c r="B8">
+        <v>20</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8" s="14"/>
+      <c r="L8" t="str">
+        <v>Bakery</v>
+      </c>
+      <c r="M8" t="str">
+        <v>Desserts</v>
+      </c>
+      <c r="N8">
+        <v>25000</v>
+      </c>
+      <c r="O8">
+        <v>80000</v>
+      </c>
+      <c r="P8">
+        <v>120000</v>
+      </c>
+      <c r="W8" t="str">
+        <v>Beef</v>
+      </c>
+      <c r="X8">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD8" s="32" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A9" t="str">
+        <v>Bananas</v>
+      </c>
+      <c r="B9">
+        <v>60</v>
+      </c>
+      <c r="E9" t="str" cm="1">
+        <f t="array" ref="E9:F14">[1]!Items</f>
+        <v>Item</v>
+      </c>
+      <c r="F9" t="str">
+        <v>Amount</v>
+      </c>
+      <c r="L9" t="str">
+        <v>Meat</v>
+      </c>
+      <c r="M9" t="str">
+        <v>Beef</v>
+      </c>
+      <c r="N9">
+        <v>90000</v>
+      </c>
+      <c r="O9">
+        <v>110000</v>
+      </c>
+      <c r="P9">
+        <v>120000</v>
+      </c>
+      <c r="W9" t="str">
+        <v>Bananas</v>
+      </c>
+      <c r="X9">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>70</v>
+      </c>
+      <c r="AD9" s="32" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A10" t="str">
+        <v>Lemons</v>
+      </c>
+      <c r="B10">
+        <v>40</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Bread</v>
+      </c>
+      <c r="F10">
+        <v>50</v>
+      </c>
+      <c r="L10" t="str">
+        <v>Produce</v>
+      </c>
+      <c r="M10" t="str">
+        <v>Fruit</v>
+      </c>
+      <c r="N10">
+        <v>10000</v>
+      </c>
+      <c r="O10">
+        <v>30000</v>
+      </c>
+      <c r="P10">
+        <v>40000</v>
+      </c>
+      <c r="W10" t="str">
+        <v>Lemons</v>
+      </c>
+      <c r="X10">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>71</v>
+      </c>
+      <c r="AD10" s="32" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="B11">
+        <f>SUM(B7:B10)</f>
+        <v>170</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Donuts</v>
+      </c>
+      <c r="F11">
+        <v>100</v>
+      </c>
+      <c r="L11" t="str">
+        <v>Produce</v>
+      </c>
+      <c r="M11" t="str">
+        <v>Veggies</v>
+      </c>
+      <c r="N11">
+        <v>30000</v>
+      </c>
+      <c r="O11">
+        <v>80000</v>
+      </c>
+      <c r="P11">
+        <v>30000</v>
+      </c>
+      <c r="W11" t="str">
+        <v>Broccoli</v>
+      </c>
+      <c r="X11">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>72</v>
+      </c>
+      <c r="AD11" s="32" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="E12" t="str">
+        <v>Cookies</v>
+      </c>
+      <c r="F12">
+        <v>40</v>
+      </c>
+      <c r="L12" t="str">
+        <v>Deli</v>
+      </c>
+      <c r="M12" t="str">
+        <v>Salads</v>
+      </c>
+      <c r="N12">
+        <v>90000</v>
+      </c>
+      <c r="O12">
+        <v>35000</v>
+      </c>
+      <c r="P12">
+        <v>25000</v>
+      </c>
+      <c r="W12" t="str">
+        <v>Kale</v>
+      </c>
+      <c r="X12">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>74</v>
+      </c>
+      <c r="AD12" s="32" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A13" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="12"/>
+      <c r="E13" t="str">
+        <v>Cakes</v>
+      </c>
+      <c r="F13">
+        <v>50</v>
+      </c>
+      <c r="L13" t="str">
+        <v>Bakery</v>
+      </c>
+      <c r="M13" t="str">
+        <v>Breads</v>
+      </c>
+      <c r="N13">
+        <v>30000</v>
+      </c>
+      <c r="O13">
+        <v>15000</v>
+      </c>
+      <c r="P13">
+        <v>20000</v>
+      </c>
+      <c r="W13" t="str">
+        <v>Ham</v>
+      </c>
+      <c r="X13">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="s">
+        <v>73</v>
+      </c>
+      <c r="AB13" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD13" s="32" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A14" t="str" cm="1">
+        <f t="array" ref="A14:B18">[1]!Meat</f>
+        <v>Meat</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Amount</v>
+      </c>
+      <c r="E14" t="str">
+        <v>Pies</v>
+      </c>
+      <c r="F14">
+        <v>20</v>
+      </c>
+      <c r="L14" t="str">
+        <v>Deli</v>
+      </c>
+      <c r="M14" t="str">
+        <v>Sandwiches</v>
+      </c>
+      <c r="N14">
+        <v>80000</v>
+      </c>
+      <c r="O14">
+        <v>40000</v>
+      </c>
+      <c r="P14">
+        <v>20000</v>
+      </c>
+      <c r="W14" t="str">
+        <v>Bread</v>
+      </c>
+      <c r="X14">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD14" s="32" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A15" t="str">
+        <v>Beef</v>
+      </c>
+      <c r="B15">
+        <v>50</v>
+      </c>
+      <c r="F15">
+        <f>SUMIF(F10:F14,"&gt;50")</f>
+        <v>100</v>
+      </c>
+      <c r="W15" t="str">
+        <v>Chicken</v>
+      </c>
+      <c r="X15">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="s">
+        <v>75</v>
+      </c>
+      <c r="AD15" s="32" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A16" t="str">
+        <v>Chicken</v>
+      </c>
+      <c r="B16">
+        <v>30</v>
+      </c>
+      <c r="W16" t="str">
+        <v>Cookies</v>
+      </c>
+      <c r="X16">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD16" s="32" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="17" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A17" t="str">
+        <v>Pork</v>
+      </c>
+      <c r="B17">
+        <v>10</v>
+      </c>
+      <c r="G17" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="H17" s="12"/>
+      <c r="W17" t="str">
+        <v>Cakes</v>
+      </c>
+      <c r="X17">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD17" s="32" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="18" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A18" t="str">
+        <v>Fish</v>
+      </c>
+      <c r="B18">
+        <v>50</v>
+      </c>
+      <c r="G18" t="str" cm="1">
+        <f t="array" ref="G18:H23">[1]!ExtraCredit</f>
+        <v>Item</v>
+      </c>
+      <c r="H18" t="str">
+        <v>Amount</v>
+      </c>
+      <c r="L18" t="str" cm="1">
+        <f t="array" aca="1" ref="L18:O24" ca="1">[1]!Sort[#All]</f>
+        <v>Expense date</v>
+      </c>
+      <c r="M18" t="str">
+        <f ca="1"/>
+        <v>Employee</v>
+      </c>
+      <c r="N18" t="str">
+        <f ca="1"/>
+        <v>Food</v>
+      </c>
+      <c r="O18" t="str">
+        <f ca="1"/>
+        <v>Hotel</v>
+      </c>
+      <c r="W18" t="str">
+        <v>Pies</v>
+      </c>
+      <c r="X18">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="s">
+        <v>40</v>
+      </c>
+      <c r="AD18" s="32" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="19" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="B19">
+        <f xml:space="preserve"> SUM(B15:B18)</f>
+        <v>140</v>
+      </c>
+      <c r="G19" t="str">
+        <v>Bread</v>
+      </c>
+      <c r="H19">
+        <v>50</v>
+      </c>
+      <c r="L19">
+        <f ca="1"/>
+        <v>46034</v>
+      </c>
+      <c r="M19" t="str">
+        <f ca="1"/>
+        <v>Laura</v>
+      </c>
+      <c r="N19">
+        <f ca="1"/>
+        <v>45</v>
+      </c>
+      <c r="O19">
+        <f ca="1"/>
+        <v>5050</v>
+      </c>
+    </row>
+    <row r="20" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G20" t="str">
+        <v>Donuts</v>
+      </c>
+      <c r="H20">
+        <v>100</v>
+      </c>
+      <c r="L20">
+        <f ca="1"/>
+        <v>46037</v>
+      </c>
+      <c r="M20" t="str">
+        <f ca="1"/>
+        <v>Jackie</v>
+      </c>
+      <c r="N20">
+        <f ca="1"/>
+        <v>21</v>
+      </c>
+      <c r="O20">
+        <f ca="1"/>
+        <v>3820</v>
+      </c>
+      <c r="AC20" s="31" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="21" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="G21" t="str">
+        <v>Cookies</v>
+      </c>
+      <c r="H21">
+        <v>40</v>
+      </c>
+      <c r="L21">
+        <f ca="1"/>
+        <v>46039</v>
+      </c>
+      <c r="M21" t="str">
+        <f ca="1"/>
+        <v>Tricia</v>
+      </c>
+      <c r="N21">
+        <f ca="1"/>
+        <v>30</v>
+      </c>
+      <c r="O21">
+        <f ca="1"/>
+        <v>3085</v>
+      </c>
+      <c r="AC21" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="22" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="G22" t="str">
+        <v>Cakes</v>
+      </c>
+      <c r="H22">
+        <v>50</v>
+      </c>
+      <c r="L22">
+        <f ca="1"/>
+        <v>46033</v>
+      </c>
+      <c r="M22" t="str">
+        <f ca="1"/>
+        <v>Dave</v>
+      </c>
+      <c r="N22">
+        <f ca="1"/>
+        <v>25</v>
+      </c>
+      <c r="O22">
+        <f ca="1"/>
+        <v>1611</v>
+      </c>
+      <c r="AC22" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="23" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="G23" t="str">
+        <v>Pies</v>
+      </c>
+      <c r="H23">
+        <v>20</v>
+      </c>
+      <c r="L23">
+        <f ca="1"/>
+        <v>46035</v>
+      </c>
+      <c r="M23" t="str">
+        <f ca="1"/>
+        <v>Jeff</v>
+      </c>
+      <c r="N23">
+        <f ca="1"/>
+        <v>69</v>
+      </c>
+      <c r="O23">
+        <f ca="1"/>
+        <v>528</v>
+      </c>
+      <c r="AC23" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="24" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="H24">
+        <f>SUMIF(H19:H23,"&lt;100")</f>
+        <v>160</v>
+      </c>
+      <c r="L24">
+        <f ca="1"/>
+        <v>46036</v>
+      </c>
+      <c r="M24" t="str">
+        <f ca="1"/>
+        <v>Mark</v>
+      </c>
+      <c r="N24">
+        <f ca="1"/>
+        <v>62</v>
+      </c>
+      <c r="O24">
+        <f ca="1"/>
+        <v>2112</v>
+      </c>
+      <c r="AC24" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="25" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A25" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="B25" s="18"/>
+      <c r="C25" s="18"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="18"/>
+      <c r="G25" s="18"/>
+      <c r="H25" s="18"/>
+      <c r="AC25" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="26" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AC26" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="27" spans="1:33" ht="30" x14ac:dyDescent="0.7">
+      <c r="A27" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="B27" s="16"/>
+      <c r="C27" s="16"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="16"/>
+      <c r="F27" s="16"/>
+      <c r="G27" s="16"/>
+      <c r="H27" s="16"/>
+      <c r="I27" s="16"/>
+      <c r="J27" s="16"/>
+      <c r="K27" s="16"/>
+      <c r="U27" s="34" t="s">
+        <v>84</v>
+      </c>
+      <c r="V27" s="33"/>
+      <c r="W27" s="33"/>
+      <c r="X27" s="33"/>
+      <c r="Y27" s="33"/>
+      <c r="Z27" s="33"/>
+      <c r="AA27" s="33"/>
+      <c r="AB27" s="33"/>
+      <c r="AC27" s="33"/>
+      <c r="AD27" s="33"/>
+      <c r="AE27" s="33"/>
+      <c r="AF27" s="33"/>
+      <c r="AG27" s="33"/>
+    </row>
+    <row r="28" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="B28" t="str">
+        <f>B51</f>
+        <v>Flash Fill - Ctrl + E</v>
+      </c>
+      <c r="M28" t="str" cm="1">
+        <f t="array" aca="1" ref="M28:P33" ca="1">'[1]5. Sort &amp; filter'!$C$49:$F$54</f>
+        <v>Expense date</v>
+      </c>
+      <c r="N28" t="str">
+        <f ca="1"/>
+        <v>Employee</v>
+      </c>
+      <c r="O28" t="str">
+        <f ca="1"/>
+        <v>Food</v>
+      </c>
+      <c r="P28" t="str">
+        <f ca="1"/>
+        <v>Hotel</v>
+      </c>
+    </row>
+    <row r="29" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="M29">
+        <f ca="1"/>
+        <v>46037</v>
+      </c>
+      <c r="N29" t="str">
+        <f ca="1"/>
+        <v>Jackie</v>
+      </c>
+      <c r="O29">
+        <f ca="1"/>
+        <v>21</v>
+      </c>
+      <c r="P29">
+        <f ca="1"/>
+        <v>3820</v>
+      </c>
+    </row>
+    <row r="30" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A30" t="str" cm="1">
+        <f t="array" ref="A30:E34">'[1]2. Fill'!$C$3:$G$7</f>
+        <v>This:</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Plus this:</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Equals:</v>
+      </c>
+      <c r="D30" t="str">
+        <v>Plus this:</v>
+      </c>
+      <c r="E30" t="str">
+        <v>Equals:</v>
+      </c>
+      <c r="G30" t="str" cm="1">
+        <f t="array" ref="G30:K35">'[1]2. Fill'!$C$10:$G$15</f>
+        <v>This:</v>
+      </c>
+      <c r="H30" t="str">
+        <v>Plus this:</v>
+      </c>
+      <c r="I30" t="str">
+        <v>Equals:</v>
+      </c>
+      <c r="J30" t="str">
+        <v>Plus this:</v>
+      </c>
+      <c r="K30" t="str">
+        <v>Equals:</v>
+      </c>
+      <c r="M30">
+        <f ca="1"/>
+        <v>46036</v>
+      </c>
+      <c r="N30" t="str">
+        <f ca="1"/>
+        <v>Mark</v>
+      </c>
+      <c r="O30">
+        <f ca="1"/>
+        <v>62</v>
+      </c>
+      <c r="P30">
+        <f ca="1"/>
+        <v>2112</v>
+      </c>
+    </row>
+    <row r="31" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>50</v>
+      </c>
+      <c r="B31">
+        <v>50</v>
+      </c>
+      <c r="C31">
+        <v>100</v>
+      </c>
+      <c r="D31">
+        <v>75</v>
+      </c>
+      <c r="E31">
+        <v>175</v>
+      </c>
+      <c r="G31">
+        <v>50</v>
+      </c>
+      <c r="H31">
+        <v>50</v>
+      </c>
+      <c r="I31">
+        <v>100</v>
+      </c>
+      <c r="J31">
+        <v>75</v>
+      </c>
+      <c r="K31">
+        <v>175</v>
+      </c>
+      <c r="M31">
+        <f ca="1"/>
+        <v>46039</v>
+      </c>
+      <c r="N31" t="str">
+        <f ca="1"/>
+        <v>Tricia</v>
+      </c>
+      <c r="O31">
+        <f ca="1"/>
+        <v>30</v>
+      </c>
+      <c r="P31">
+        <f ca="1"/>
+        <v>3085</v>
+      </c>
+      <c r="V31" t="s">
+        <v>79</v>
+      </c>
+      <c r="W31" t="s">
+        <v>85</v>
+      </c>
+      <c r="X31" t="s">
+        <v>86</v>
+      </c>
+      <c r="Y31" t="s">
+        <v>87</v>
+      </c>
+      <c r="Z31" t="s">
+        <v>88</v>
+      </c>
+      <c r="AC31" t="str" cm="1">
+        <f t="array" ref="AC31:AG39">[1]!AnalyzeData[#All]</f>
+        <v>Department</v>
+      </c>
+      <c r="AD31" t="str">
+        <v>Category</v>
+      </c>
+      <c r="AE31" t="str">
+        <v>Oct</v>
+      </c>
+      <c r="AF31" t="str">
+        <v>Nov</v>
+      </c>
+      <c r="AG31" t="str">
+        <v>Dec</v>
+      </c>
+    </row>
+    <row r="32" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <v>50</v>
+      </c>
+      <c r="B32">
+        <v>60</v>
+      </c>
+      <c r="C32">
+        <v>110</v>
+      </c>
+      <c r="D32">
+        <v>75</v>
+      </c>
+      <c r="E32">
+        <v>185</v>
+      </c>
+      <c r="G32">
+        <v>50</v>
+      </c>
+      <c r="H32">
+        <v>60</v>
+      </c>
+      <c r="I32">
+        <v>110</v>
+      </c>
+      <c r="J32">
+        <v>75</v>
+      </c>
+      <c r="K32">
+        <v>185</v>
+      </c>
+      <c r="M32">
+        <f ca="1"/>
+        <v>46033</v>
+      </c>
+      <c r="N32" t="str">
+        <f ca="1"/>
+        <v>Dave</v>
+      </c>
+      <c r="O32">
+        <f ca="1"/>
+        <v>25</v>
+      </c>
+      <c r="P32">
+        <f ca="1"/>
+        <v>1611</v>
+      </c>
+      <c r="V32" t="s">
+        <v>76</v>
+      </c>
+      <c r="W32" t="s">
+        <v>91</v>
+      </c>
+      <c r="X32">
+        <v>30000</v>
+      </c>
+      <c r="Y32" s="35">
+        <v>15000</v>
+      </c>
+      <c r="Z32" s="35">
+        <v>20000</v>
+      </c>
+      <c r="AC32" t="str">
+        <v>Produce</v>
+      </c>
+      <c r="AD32" t="str">
+        <v>Veggies</v>
+      </c>
+      <c r="AE32">
+        <v>30000</v>
+      </c>
+      <c r="AF32">
+        <v>80000</v>
+      </c>
+      <c r="AG32">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="33" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A33">
+        <v>50</v>
+      </c>
+      <c r="B33">
+        <v>70</v>
+      </c>
+      <c r="C33">
+        <v>120</v>
+      </c>
+      <c r="D33">
+        <v>75</v>
+      </c>
+      <c r="E33">
+        <v>195</v>
+      </c>
+      <c r="G33">
+        <v>50</v>
+      </c>
+      <c r="H33">
+        <v>70</v>
+      </c>
+      <c r="I33">
+        <v>120</v>
+      </c>
+      <c r="J33">
+        <v>75</v>
+      </c>
+      <c r="K33">
+        <v>195</v>
+      </c>
+      <c r="M33">
+        <f ca="1"/>
+        <v>46034</v>
+      </c>
+      <c r="N33" t="str">
+        <f ca="1"/>
+        <v>Laura</v>
+      </c>
+      <c r="O33">
+        <f ca="1"/>
+        <v>45</v>
+      </c>
+      <c r="P33">
+        <f ca="1"/>
+        <v>5050</v>
+      </c>
+      <c r="V33" t="s">
+        <v>93</v>
+      </c>
+      <c r="W33" t="s">
+        <v>94</v>
+      </c>
+      <c r="X33">
+        <v>30000</v>
+      </c>
+      <c r="Y33" s="35">
+        <v>40000</v>
+      </c>
+      <c r="Z33" s="35">
+        <v>20000</v>
+      </c>
+      <c r="AC33" t="str">
+        <v>Produce</v>
+      </c>
+      <c r="AD33" t="str">
+        <v>Fruit</v>
+      </c>
+      <c r="AE33">
+        <v>10000</v>
+      </c>
+      <c r="AF33">
+        <v>30000</v>
+      </c>
+      <c r="AG33">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="34" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A34">
+        <v>50</v>
+      </c>
+      <c r="B34">
+        <v>80</v>
+      </c>
+      <c r="C34">
+        <v>130</v>
+      </c>
+      <c r="D34">
+        <v>75</v>
+      </c>
+      <c r="E34">
+        <v>205</v>
+      </c>
+      <c r="G34">
+        <v>50</v>
+      </c>
+      <c r="H34">
+        <v>80</v>
+      </c>
+      <c r="I34">
+        <v>130</v>
+      </c>
+      <c r="J34">
+        <v>75</v>
+      </c>
+      <c r="K34">
+        <v>205</v>
+      </c>
+      <c r="V34" t="s">
+        <v>93</v>
+      </c>
+      <c r="W34" t="s">
+        <v>95</v>
+      </c>
+      <c r="X34">
+        <v>30000</v>
+      </c>
+      <c r="Y34" s="35">
+        <v>35000</v>
+      </c>
+      <c r="Z34" s="35">
+        <v>25000</v>
+      </c>
+      <c r="AC34" t="str">
+        <v>Bakery</v>
+      </c>
+      <c r="AD34" t="str">
+        <v>Breads</v>
+      </c>
+      <c r="AE34">
+        <v>30000</v>
+      </c>
+      <c r="AF34">
+        <v>15000</v>
+      </c>
+      <c r="AG34">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="35" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="G35">
+        <v>200</v>
+      </c>
+      <c r="H35">
+        <v>260</v>
+      </c>
+      <c r="I35">
+        <v>460</v>
+      </c>
+      <c r="J35">
+        <v>300</v>
+      </c>
+      <c r="K35">
+        <v>760</v>
+      </c>
+      <c r="V35" t="s">
+        <v>66</v>
+      </c>
+      <c r="W35" t="s">
+        <v>89</v>
+      </c>
+      <c r="X35">
+        <v>30000</v>
+      </c>
+      <c r="Y35" s="35">
+        <v>80000</v>
+      </c>
+      <c r="Z35" s="35">
+        <v>30000</v>
+      </c>
+      <c r="AC35" t="str">
+        <v>Bakery</v>
+      </c>
+      <c r="AD35" t="str">
+        <v>Desserts</v>
+      </c>
+      <c r="AE35">
+        <v>25000</v>
+      </c>
+      <c r="AF35">
+        <v>80000</v>
+      </c>
+      <c r="AG35">
+        <v>120000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="M36" t="str" cm="1">
+        <f t="array" aca="1" ref="M36:P41" ca="1">'[1]5. Sort &amp; filter'!$C$49:$F$54</f>
+        <v>Expense date</v>
+      </c>
+      <c r="N36" t="str">
+        <f ca="1"/>
+        <v>Employee</v>
+      </c>
+      <c r="O36" t="str">
+        <f ca="1"/>
+        <v>Food</v>
+      </c>
+      <c r="P36" t="str">
+        <f ca="1"/>
+        <v>Hotel</v>
+      </c>
+      <c r="V36" t="s">
+        <v>66</v>
+      </c>
+      <c r="W36" t="s">
+        <v>90</v>
+      </c>
+      <c r="X36">
+        <v>30000</v>
+      </c>
+      <c r="Y36" s="35">
+        <v>30000</v>
+      </c>
+      <c r="Z36" s="35">
+        <v>40000</v>
+      </c>
+      <c r="AC36" t="str">
+        <v>Deli</v>
+      </c>
+      <c r="AD36" t="str">
+        <v>Sandwich</v>
+      </c>
+      <c r="AE36">
+        <v>80000</v>
+      </c>
+      <c r="AF36">
+        <v>40000</v>
+      </c>
+      <c r="AG36">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="37" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="M37">
+        <f ca="1"/>
+        <v>46037</v>
+      </c>
+      <c r="N37" t="str">
+        <f ca="1"/>
+        <v>Jackie</v>
+      </c>
+      <c r="O37">
+        <f ca="1"/>
+        <v>21</v>
+      </c>
+      <c r="P37">
+        <f ca="1"/>
+        <v>3820</v>
+      </c>
+      <c r="V37" t="s">
+        <v>76</v>
+      </c>
+      <c r="W37" t="s">
+        <v>92</v>
+      </c>
+      <c r="X37">
+        <v>30000</v>
+      </c>
+      <c r="Y37" s="35">
+        <v>80000</v>
+      </c>
+      <c r="Z37" s="35">
+        <v>120000</v>
+      </c>
+      <c r="AC37" t="str">
+        <v>Deli</v>
+      </c>
+      <c r="AD37" t="str">
+        <v>Salads</v>
+      </c>
+      <c r="AE37">
+        <v>90000</v>
+      </c>
+      <c r="AF37">
+        <v>35000</v>
+      </c>
+      <c r="AG37">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="38" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="B38" t="str" cm="1">
+        <f t="array" ref="B38:E42">'[1]2. Fill'!$C$33:$F$37</f>
+        <v>Dept.</v>
+      </c>
+      <c r="C38" t="str">
+        <v>Category</v>
+      </c>
+      <c r="D38" t="str">
+        <v>Product</v>
+      </c>
+      <c r="E38" t="str">
+        <v>Count</v>
+      </c>
+      <c r="H38" t="str" cm="1">
+        <f t="array" ref="H38:H41">'[1]2. Fill'!$H$47:$H$50</f>
+        <v>Qrtr 1</v>
+      </c>
+      <c r="M38">
+        <f ca="1"/>
+        <v>46036</v>
+      </c>
+      <c r="N38" t="str">
+        <f ca="1"/>
+        <v>Mark</v>
+      </c>
+      <c r="O38">
+        <f ca="1"/>
+        <v>62</v>
+      </c>
+      <c r="P38">
+        <f ca="1"/>
+        <v>2112</v>
+      </c>
+      <c r="V38" t="s">
+        <v>80</v>
+      </c>
+      <c r="W38" t="s">
+        <v>75</v>
+      </c>
+      <c r="X38">
+        <v>30000</v>
+      </c>
+      <c r="Y38" s="35">
+        <v>82000</v>
+      </c>
+      <c r="Z38" s="35">
+        <v>150000</v>
+      </c>
+      <c r="AC38" t="str">
+        <v>Meat</v>
+      </c>
+      <c r="AD38" t="str">
+        <v>Beef</v>
+      </c>
+      <c r="AE38">
+        <v>90000</v>
+      </c>
+      <c r="AF38">
+        <v>110000</v>
+      </c>
+      <c r="AG38">
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="B39" t="str">
+        <v>Produce</v>
+      </c>
+      <c r="C39" t="str">
+        <v>Fruit</v>
+      </c>
+      <c r="D39" t="str">
+        <v>Apple</v>
+      </c>
+      <c r="E39">
+        <v>100</v>
+      </c>
+      <c r="H39" t="str">
+        <v>Qrtr 2</v>
+      </c>
+      <c r="M39">
+        <f ca="1"/>
+        <v>46039</v>
+      </c>
+      <c r="N39" t="str">
+        <f ca="1"/>
+        <v>Tricia</v>
+      </c>
+      <c r="O39">
+        <f ca="1"/>
+        <v>30</v>
+      </c>
+      <c r="P39">
+        <f ca="1"/>
+        <v>3085</v>
+      </c>
+      <c r="V39" t="s">
+        <v>80</v>
+      </c>
+      <c r="W39" t="s">
+        <v>70</v>
+      </c>
+      <c r="X39">
+        <v>30000</v>
+      </c>
+      <c r="Y39" s="35">
+        <v>110000</v>
+      </c>
+      <c r="Z39" s="35">
+        <v>200000</v>
+      </c>
+      <c r="AC39" t="str">
+        <v>Meat</v>
+      </c>
+      <c r="AD39" t="str">
+        <v>Chicken</v>
+      </c>
+      <c r="AE39">
+        <v>75000</v>
+      </c>
+      <c r="AF39">
+        <v>82000</v>
+      </c>
+      <c r="AG39">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="40" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B40" t="str">
+        <v>Produce</v>
+      </c>
+      <c r="C40" t="str">
+        <v>Fruit</v>
+      </c>
+      <c r="D40" t="str">
+        <v>Orange</v>
+      </c>
+      <c r="E40">
+        <v>200</v>
+      </c>
+      <c r="H40" t="str">
+        <v>Qrtr 3</v>
+      </c>
+      <c r="M40">
+        <f ca="1"/>
+        <v>46033</v>
+      </c>
+      <c r="N40" t="str">
+        <f ca="1"/>
+        <v>Dave</v>
+      </c>
+      <c r="O40">
+        <f ca="1"/>
+        <v>25</v>
+      </c>
+      <c r="P40">
+        <f ca="1"/>
+        <v>1611</v>
+      </c>
+      <c r="X40">
+        <v>30000</v>
+      </c>
+      <c r="Y40" s="35"/>
+      <c r="Z40" s="35"/>
+    </row>
+    <row r="41" spans="1:33" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B41" t="str">
+        <v>Produce</v>
+      </c>
+      <c r="C41" t="str">
+        <v>Fruit</v>
+      </c>
+      <c r="D41" t="str">
+        <v>Banana</v>
+      </c>
+      <c r="E41">
+        <v>50</v>
+      </c>
+      <c r="H41" t="str">
+        <v>Qrtr 4</v>
+      </c>
+      <c r="M41">
+        <f ca="1"/>
+        <v>46034</v>
+      </c>
+      <c r="N41" t="str">
+        <f ca="1"/>
+        <v>Laura</v>
+      </c>
+      <c r="O41">
+        <f ca="1"/>
+        <v>45</v>
+      </c>
+      <c r="P41">
+        <f ca="1"/>
+        <v>5050</v>
+      </c>
+      <c r="X41">
+        <v>30000</v>
+      </c>
+      <c r="Y41" s="35"/>
+      <c r="Z41" s="35"/>
+    </row>
+    <row r="42" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="B42" t="str">
+        <v>Produce</v>
+      </c>
+      <c r="C42" t="str">
+        <v>Fruit</v>
+      </c>
+      <c r="D42" t="str">
+        <v>Pears</v>
+      </c>
+      <c r="E42">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="45" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A45" t="str" cm="1">
+        <f t="array" ref="A45:F46">'[1]2. Fill'!$C$60:$H$61</f>
+        <v>Intervals</v>
+      </c>
+      <c r="B45">
+        <v>0</v>
+      </c>
+      <c r="C45">
+        <v>0</v>
+      </c>
+      <c r="D45">
+        <v>0</v>
+      </c>
+      <c r="E45">
+        <v>0</v>
+      </c>
+      <c r="F45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A46">
+        <v>15</v>
+      </c>
+      <c r="B46">
+        <v>30</v>
+      </c>
+      <c r="C46">
+        <v>45</v>
+      </c>
+      <c r="D46">
+        <v>60</v>
+      </c>
+      <c r="E46">
+        <v>75</v>
+      </c>
+      <c r="F46">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="49" spans="1:33" ht="30" x14ac:dyDescent="0.7">
+      <c r="A49" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="B49" s="19"/>
+      <c r="C49" s="19"/>
+      <c r="D49" s="19"/>
+      <c r="E49" s="19"/>
+      <c r="F49" s="19"/>
+      <c r="G49" s="19"/>
+      <c r="H49" s="19"/>
+      <c r="I49" s="19"/>
+      <c r="J49" s="19"/>
+      <c r="K49" s="19"/>
+      <c r="M49" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="N49" s="28"/>
+      <c r="O49" s="28"/>
+      <c r="P49" s="28"/>
+      <c r="Q49" s="28"/>
+      <c r="V49" s="39" t="s">
+        <v>98</v>
+      </c>
+      <c r="W49" s="38"/>
+      <c r="X49" s="38"/>
+      <c r="Y49" s="38"/>
+      <c r="Z49" s="38"/>
+      <c r="AA49" s="38"/>
+      <c r="AB49" s="38"/>
+      <c r="AC49" s="38"/>
+      <c r="AD49" s="38"/>
+      <c r="AE49" s="38"/>
+      <c r="AF49" s="38"/>
+      <c r="AG49" s="38"/>
+    </row>
+    <row r="51" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="B51" t="s">
+        <v>34</v>
+      </c>
+      <c r="M51" t="str" cm="1">
+        <f t="array" ref="M51:Q60">'[1]6. Tables'!$C$5:$G$14</f>
+        <v>Department</v>
+      </c>
+      <c r="N51" t="str">
+        <v>Category</v>
+      </c>
+      <c r="O51" t="str">
+        <v>Oct</v>
+      </c>
+      <c r="P51" t="str">
+        <v>Nov</v>
+      </c>
+      <c r="Q51" t="str">
+        <v>Dec</v>
+      </c>
+      <c r="X51" t="str" cm="1">
+        <f t="array" aca="1" ref="X51:Y57" ca="1">[1]!RecommendedChartData[#All]</f>
+        <v>Year</v>
+      </c>
+      <c r="Y51" t="str">
+        <f ca="1"/>
+        <v>Conference attendance</v>
+      </c>
+    </row>
+    <row r="52" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A52" t="str" cm="1">
+        <f t="array" ref="A52:C57">'[1]3. Split'!$C$4:$E$9</f>
+        <v>Email</v>
+      </c>
+      <c r="B52" t="str">
+        <v>First name</v>
+      </c>
+      <c r="C52" t="str">
+        <v>Last name</v>
+      </c>
+      <c r="M52" t="str">
+        <v>Produce</v>
+      </c>
+      <c r="N52" t="str">
+        <v>Veggies</v>
+      </c>
+      <c r="O52">
+        <v>30000</v>
+      </c>
+      <c r="P52">
+        <v>80000</v>
+      </c>
+      <c r="Q52">
+        <v>30000</v>
+      </c>
+      <c r="X52">
+        <f ca="1"/>
+        <v>2021</v>
+      </c>
+      <c r="Y52">
+        <f ca="1"/>
+        <v>500</v>
+      </c>
+    </row>
+    <row r="53" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A53" t="str">
+        <v>Nancy.Smith@contoso.com</v>
+      </c>
+      <c r="B53" t="str">
+        <v>Nancy</v>
+      </c>
+      <c r="C53" t="str">
+        <v>Smith</v>
+      </c>
+      <c r="M53" t="str">
+        <v>Produce</v>
+      </c>
+      <c r="N53" t="str">
+        <v>Fruit</v>
+      </c>
+      <c r="O53">
+        <v>10000</v>
+      </c>
+      <c r="P53">
+        <v>30000</v>
+      </c>
+      <c r="Q53">
+        <v>40000</v>
+      </c>
+      <c r="X53">
+        <f ca="1"/>
+        <v>2022</v>
+      </c>
+      <c r="Y53">
+        <f ca="1"/>
+        <v>800</v>
+      </c>
+    </row>
+    <row r="54" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A54" t="str">
+        <v>Andy.North@fabrikam.com</v>
+      </c>
+      <c r="B54" t="str">
+        <v>Andy</v>
+      </c>
+      <c r="C54" t="str">
+        <v>North</v>
+      </c>
+      <c r="M54" t="str">
+        <v>Bakery</v>
+      </c>
+      <c r="N54" t="str">
+        <v>Breads</v>
+      </c>
+      <c r="O54">
+        <v>30000</v>
+      </c>
+      <c r="P54">
+        <v>15000</v>
+      </c>
+      <c r="Q54">
+        <v>20000</v>
+      </c>
+      <c r="X54">
+        <f ca="1"/>
+        <v>2023</v>
+      </c>
+      <c r="Y54">
+        <f ca="1"/>
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="55" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A55" t="str">
+        <v>Jan.Kotas@relecloud.com</v>
+      </c>
+      <c r="B55" t="str">
+        <v>Jan</v>
+      </c>
+      <c r="C55" t="str">
+        <v>Kotas</v>
+      </c>
+      <c r="M55" t="str">
+        <v>Bakery</v>
+      </c>
+      <c r="N55" t="str">
+        <v>Desserts</v>
+      </c>
+      <c r="O55">
+        <v>25000</v>
+      </c>
+      <c r="P55">
+        <v>80000</v>
+      </c>
+      <c r="Q55">
+        <v>120000</v>
+      </c>
+      <c r="X55">
+        <f ca="1"/>
+        <v>2024</v>
+      </c>
+      <c r="Y55">
+        <f ca="1"/>
+        <v>900</v>
+      </c>
+    </row>
+    <row r="56" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A56" t="str">
+        <v>Mariya.Jones@contoso.com</v>
+      </c>
+      <c r="B56" t="str">
+        <v>Mariya</v>
+      </c>
+      <c r="C56" t="str">
+        <v>Jones</v>
+      </c>
+      <c r="M56" t="str">
+        <v>Deli</v>
+      </c>
+      <c r="N56" t="str">
+        <v>Sandwich</v>
+      </c>
+      <c r="O56">
+        <v>80000</v>
+      </c>
+      <c r="P56">
+        <v>40000</v>
+      </c>
+      <c r="Q56">
+        <v>20000</v>
+      </c>
+      <c r="X56">
+        <f ca="1"/>
+        <v>2025</v>
+      </c>
+      <c r="Y56">
+        <f ca="1"/>
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="57" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A57" t="str">
+        <v xml:space="preserve">Yvonne.McKay@fabrikam.com </v>
+      </c>
+      <c r="B57" t="str">
+        <v>Yvonne</v>
+      </c>
+      <c r="C57" t="str">
+        <v>McKay</v>
+      </c>
+      <c r="M57" t="str">
+        <v>Deli</v>
+      </c>
+      <c r="N57" t="str">
+        <v>Salads</v>
+      </c>
+      <c r="O57">
+        <v>90000</v>
+      </c>
+      <c r="P57">
+        <v>35000</v>
+      </c>
+      <c r="Q57">
+        <v>25000</v>
+      </c>
+      <c r="X57">
+        <f ca="1"/>
+        <v>2026</v>
+      </c>
+      <c r="Y57">
+        <f ca="1"/>
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="58" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="M58" t="str">
+        <v>Meat</v>
+      </c>
+      <c r="N58" t="str">
+        <v>Beef</v>
+      </c>
+      <c r="O58">
+        <v>90000</v>
+      </c>
+      <c r="P58">
+        <v>110000</v>
+      </c>
+      <c r="Q58">
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="59" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="M59" t="str">
+        <v>Meat</v>
+      </c>
+      <c r="N59" t="str">
+        <v>Chicken</v>
+      </c>
+      <c r="O59">
+        <v>75000</v>
+      </c>
+      <c r="P59">
+        <v>82000</v>
+      </c>
+      <c r="Q59">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="60" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A60" t="str" cm="1">
+        <f t="array" ref="A60:D68">'[1]3. Split'!$C$31:$F$39</f>
+        <v>Data</v>
+      </c>
+      <c r="B60" t="str">
+        <v>First name</v>
+      </c>
+      <c r="C60" t="str">
+        <v>Last name</v>
+      </c>
+      <c r="D60" t="str">
+        <v>Company name</v>
+      </c>
+      <c r="M60" t="str">
+        <v>rice</v>
+      </c>
+      <c r="N60">
+        <v>0</v>
+      </c>
+      <c r="O60">
+        <v>0</v>
+      </c>
+      <c r="P60">
+        <v>0</v>
+      </c>
+      <c r="Q60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A61" t="str">
+        <v>Nancy,Smith,Contoso Ltd.</v>
+      </c>
+      <c r="B61" t="str">
+        <v>Nancy</v>
+      </c>
+      <c r="C61" t="str">
+        <v>Smith</v>
+      </c>
+      <c r="D61" t="str">
+        <v>Contoso Ltd.</v>
+      </c>
+    </row>
+    <row r="62" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A62" t="str">
+        <v>Andy,North,Fabrikam Inc.</v>
+      </c>
+      <c r="B62" t="str">
+        <v>Andy</v>
+      </c>
+      <c r="C62" t="str">
+        <v>North</v>
+      </c>
+      <c r="D62" t="str">
+        <v>Fabrikam Inc.</v>
+      </c>
+      <c r="M62" t="str" cm="1">
+        <f t="array" ref="M62:Q71">'[1]6. Tables'!$C$5:$G$14</f>
+        <v>Department</v>
+      </c>
+      <c r="N62" t="str">
+        <v>Category</v>
+      </c>
+      <c r="O62" t="str">
+        <v>Oct</v>
+      </c>
+      <c r="P62" t="str">
+        <v>Nov</v>
+      </c>
+      <c r="Q62" t="str">
+        <v>Dec</v>
+      </c>
+    </row>
+    <row r="63" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A63" t="str">
+        <v>Jan,Kotas,Relecloud</v>
+      </c>
+      <c r="B63" t="str">
+        <v>Jan</v>
+      </c>
+      <c r="C63" t="str">
+        <v>Kotas</v>
+      </c>
+      <c r="D63" t="str">
+        <v>Relecloud</v>
+      </c>
+      <c r="M63" t="str">
+        <v>Produce</v>
+      </c>
+      <c r="N63" t="str">
+        <v>Veggies</v>
+      </c>
+      <c r="O63">
+        <v>30000</v>
+      </c>
+      <c r="P63">
+        <v>80000</v>
+      </c>
+      <c r="Q63">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="64" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A64" t="str">
+        <v>Mariya,Jones,Contoso Ltd.</v>
+      </c>
+      <c r="B64" t="str">
+        <v>Mariya</v>
+      </c>
+      <c r="C64" t="str">
+        <v>Jones</v>
+      </c>
+      <c r="D64" t="str">
+        <v>Contoso Ltd.</v>
+      </c>
+      <c r="M64" t="str">
+        <v>Produce</v>
+      </c>
+      <c r="N64" t="str">
+        <v>Fruit</v>
+      </c>
+      <c r="O64">
+        <v>10000</v>
+      </c>
+      <c r="P64">
+        <v>30000</v>
+      </c>
+      <c r="Q64">
+        <v>40000</v>
+      </c>
+      <c r="V64" t="str" cm="1">
+        <f t="array" aca="1" ref="V64:X70" ca="1">[1]!RecommendedChartData2[#All]</f>
+        <v>Date</v>
+      </c>
+      <c r="W64" t="str">
+        <f ca="1"/>
+        <v>Conference attendance</v>
+      </c>
+      <c r="X64" t="str">
+        <f ca="1"/>
+        <v>Food sales</v>
+      </c>
+    </row>
+    <row r="65" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A65" t="str">
+        <v>Steven,Thorpe,Relecloud</v>
+      </c>
+      <c r="B65" t="str">
+        <v>Steven</v>
+      </c>
+      <c r="C65" t="str">
+        <v>Thorpe</v>
+      </c>
+      <c r="D65" t="str">
+        <v>Relecloud</v>
+      </c>
+      <c r="M65" t="str">
+        <v>Bakery</v>
+      </c>
+      <c r="N65" t="str">
+        <v>Breads</v>
+      </c>
+      <c r="O65">
+        <v>30000</v>
+      </c>
+      <c r="P65">
+        <v>15000</v>
+      </c>
+      <c r="Q65">
+        <v>20000</v>
+      </c>
+      <c r="V65">
+        <f ca="1"/>
+        <v>2021</v>
+      </c>
+      <c r="W65">
+        <f ca="1"/>
+        <v>500</v>
+      </c>
+      <c r="X65">
+        <f ca="1"/>
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="66" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A66" t="str">
+        <v>Michael,Neipper,Fabrikam Inc.</v>
+      </c>
+      <c r="B66" t="str">
+        <v>Michael</v>
+      </c>
+      <c r="C66" t="str">
+        <v>Neipper</v>
+      </c>
+      <c r="D66" t="str">
+        <v>Fabrikam Inc.</v>
+      </c>
+      <c r="M66" t="str">
+        <v>Bakery</v>
+      </c>
+      <c r="N66" t="str">
+        <v>Desserts</v>
+      </c>
+      <c r="O66">
+        <v>25000</v>
+      </c>
+      <c r="P66">
+        <v>80000</v>
+      </c>
+      <c r="Q66">
+        <v>120000</v>
+      </c>
+      <c r="V66">
+        <f ca="1"/>
+        <v>2022</v>
+      </c>
+      <c r="W66">
+        <f ca="1"/>
+        <v>800</v>
+      </c>
+      <c r="X66">
+        <f ca="1"/>
+        <v>11200</v>
+      </c>
+    </row>
+    <row r="67" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A67" t="str">
+        <v>Robert,Zare,Relecloud</v>
+      </c>
+      <c r="B67" t="str">
+        <v>Robert</v>
+      </c>
+      <c r="C67" t="str">
+        <v>Zare</v>
+      </c>
+      <c r="D67" t="str">
+        <v>Relecloud</v>
+      </c>
+      <c r="M67" t="str">
+        <v>Deli</v>
+      </c>
+      <c r="N67" t="str">
+        <v>Sandwich</v>
+      </c>
+      <c r="O67">
+        <v>80000</v>
+      </c>
+      <c r="P67">
+        <v>40000</v>
+      </c>
+      <c r="Q67">
+        <v>20000</v>
+      </c>
+      <c r="V67">
+        <f ca="1"/>
+        <v>2023</v>
+      </c>
+      <c r="W67">
+        <f ca="1"/>
+        <v>1000</v>
+      </c>
+      <c r="X67">
+        <f ca="1"/>
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="68" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A68" t="str">
+        <v>Yvonne,McKay,Contoso Ltd.</v>
+      </c>
+      <c r="B68" t="str">
+        <v>Yvonne</v>
+      </c>
+      <c r="C68" t="str">
+        <v>McKay</v>
+      </c>
+      <c r="D68" t="str">
+        <v>Contoso Ltd.</v>
+      </c>
+      <c r="M68" t="str">
+        <v>Deli</v>
+      </c>
+      <c r="N68" t="str">
+        <v>Salads</v>
+      </c>
+      <c r="O68">
+        <v>90000</v>
+      </c>
+      <c r="P68">
+        <v>35000</v>
+      </c>
+      <c r="Q68">
+        <v>25000</v>
+      </c>
+      <c r="V68">
+        <f ca="1"/>
+        <v>2024</v>
+      </c>
+      <c r="W68">
+        <f ca="1"/>
+        <v>900</v>
+      </c>
+      <c r="X68">
+        <f ca="1"/>
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="69" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="M69" t="str">
+        <v>Meat</v>
+      </c>
+      <c r="N69" t="str">
+        <v>Beef</v>
+      </c>
+      <c r="O69">
+        <v>90000</v>
+      </c>
+      <c r="P69">
+        <v>110000</v>
+      </c>
+      <c r="Q69">
+        <v>200000</v>
+      </c>
+      <c r="V69">
+        <f ca="1"/>
+        <v>2025</v>
+      </c>
+      <c r="W69">
+        <f ca="1"/>
+        <v>1000</v>
+      </c>
+      <c r="X69">
+        <f ca="1"/>
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="70" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="M70" t="str">
+        <v>Meat</v>
+      </c>
+      <c r="N70" t="str">
+        <v>Chicken</v>
+      </c>
+      <c r="O70">
+        <v>75000</v>
+      </c>
+      <c r="P70">
+        <v>82000</v>
+      </c>
+      <c r="Q70">
+        <v>150000</v>
+      </c>
+      <c r="V70">
+        <f ca="1"/>
+        <v>2026</v>
+      </c>
+      <c r="W70">
+        <f ca="1"/>
+        <v>1200</v>
+      </c>
+      <c r="X70">
+        <f ca="1"/>
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="71" spans="1:24" ht="27.6" x14ac:dyDescent="0.65">
+      <c r="A71" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="B71" s="16"/>
+      <c r="C71" s="16"/>
+      <c r="D71" s="16"/>
+      <c r="E71" s="16"/>
+      <c r="F71" s="16"/>
+      <c r="G71" s="16"/>
+      <c r="M71" t="str">
+        <v>rice</v>
+      </c>
+      <c r="N71">
+        <v>0</v>
+      </c>
+      <c r="O71">
+        <v>0</v>
+      </c>
+      <c r="P71">
+        <v>0</v>
+      </c>
+      <c r="Q71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A73" t="str" cm="1">
+        <f t="array" ref="A73:F74">'[1]4. Transpose'!$C$5:$H$6</f>
+        <v>Item</v>
+      </c>
+      <c r="B73" t="str">
+        <v>Bread</v>
+      </c>
+      <c r="C73" t="str">
+        <v>Donuts</v>
+      </c>
+      <c r="D73" t="str">
+        <v>Cookies</v>
+      </c>
+      <c r="E73" t="str">
+        <v>Cakes</v>
+      </c>
+      <c r="F73" t="str">
+        <v>Pies</v>
+      </c>
+    </row>
+    <row r="74" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A74" t="str">
+        <v>Amount</v>
+      </c>
+      <c r="B74">
+        <v>50</v>
+      </c>
+      <c r="C74">
+        <v>100</v>
+      </c>
+      <c r="D74">
+        <v>40</v>
+      </c>
+      <c r="E74">
+        <v>50</v>
+      </c>
+      <c r="F74">
+        <v>20</v>
+      </c>
+      <c r="M74" t="s">
+        <v>11</v>
+      </c>
+      <c r="N74" t="s">
+        <v>12</v>
+      </c>
+      <c r="O74" t="s">
+        <v>46</v>
+      </c>
+      <c r="P74" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="75" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="M75" t="s">
+        <v>47</v>
+      </c>
+      <c r="N75" t="s">
+        <v>48</v>
+      </c>
+      <c r="O75" t="s">
+        <v>49</v>
+      </c>
+      <c r="P75" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="76" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="M76" t="s">
+        <v>50</v>
+      </c>
+      <c r="N76" t="s">
+        <v>55</v>
+      </c>
+      <c r="O76" t="s">
+        <v>60</v>
+      </c>
+      <c r="P76">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="M77" t="s">
+        <v>51</v>
+      </c>
+      <c r="N77" t="s">
+        <v>56</v>
+      </c>
+      <c r="O77" t="s">
+        <v>60</v>
+      </c>
+      <c r="P77">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="78" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="B78" t="s">
+        <v>36</v>
+      </c>
+      <c r="C78" t="s">
+        <v>37</v>
+      </c>
+      <c r="D78" t="s">
+        <v>38</v>
+      </c>
+      <c r="E78" t="s">
+        <v>39</v>
+      </c>
+      <c r="F78" t="s">
+        <v>40</v>
+      </c>
+      <c r="G78" t="s">
+        <v>42</v>
+      </c>
+      <c r="M78" t="s">
+        <v>52</v>
+      </c>
+      <c r="N78" t="s">
+        <v>57</v>
+      </c>
+      <c r="O78" t="s">
+        <v>61</v>
+      </c>
+      <c r="P78">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="79" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="B79">
+        <v>50</v>
+      </c>
+      <c r="C79">
+        <v>100</v>
+      </c>
+      <c r="D79">
+        <v>40</v>
+      </c>
+      <c r="E79">
+        <v>50</v>
+      </c>
+      <c r="F79">
+        <v>20</v>
+      </c>
+      <c r="G79">
+        <v>50</v>
+      </c>
+      <c r="M79" t="s">
+        <v>53</v>
+      </c>
+      <c r="N79" t="s">
+        <v>58</v>
+      </c>
+      <c r="O79" t="s">
+        <v>61</v>
+      </c>
+      <c r="P79">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="80" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="M80" t="s">
+        <v>54</v>
+      </c>
+      <c r="N80" t="s">
+        <v>59</v>
+      </c>
+      <c r="O80" t="s">
+        <v>61</v>
+      </c>
+      <c r="P80">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="81" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B81" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="C81" s="21"/>
+      <c r="M81" t="s">
+        <v>62</v>
+      </c>
+      <c r="P81">
+        <f>SUBTOTAL(109,P75:P80)</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="82" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B82" t="s">
+        <v>36</v>
+      </c>
+      <c r="C82">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="83" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B83" t="s">
+        <v>37</v>
+      </c>
+      <c r="C83">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="84" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B84" t="s">
+        <v>38</v>
+      </c>
+      <c r="C84">
+        <v>40</v>
+      </c>
+      <c r="M84" t="str" cm="1">
+        <f t="array" ref="M84:R92">[1]!CalculatedColumns[#All]</f>
+        <v>Department</v>
+      </c>
+      <c r="N84" t="str">
+        <v>Category</v>
+      </c>
+      <c r="O84" t="str">
+        <v>Oct</v>
+      </c>
+      <c r="P84" t="str">
+        <v>Nov</v>
+      </c>
+      <c r="Q84" t="str">
+        <v>Dec</v>
+      </c>
+      <c r="R84" t="str">
+        <v>Total</v>
+      </c>
+    </row>
+    <row r="85" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B85" t="s">
+        <v>39</v>
+      </c>
+      <c r="C85">
+        <v>50</v>
+      </c>
+      <c r="M85" t="str">
+        <v>Produce</v>
+      </c>
+      <c r="N85" t="str">
+        <v>Veggies</v>
+      </c>
+      <c r="O85">
+        <v>30000</v>
+      </c>
+      <c r="P85">
+        <v>80000</v>
+      </c>
+      <c r="Q85">
+        <v>30000</v>
+      </c>
+      <c r="R85">
+        <v>140000</v>
+      </c>
+    </row>
+    <row r="86" spans="1:32" ht="30" x14ac:dyDescent="0.7">
+      <c r="B86" t="s">
+        <v>40</v>
+      </c>
+      <c r="C86">
+        <v>20</v>
+      </c>
+      <c r="M86" t="str">
+        <v>Produce</v>
+      </c>
+      <c r="N86" t="str">
+        <v>Fruit</v>
+      </c>
+      <c r="O86">
+        <v>10000</v>
+      </c>
+      <c r="P86">
+        <v>30000</v>
+      </c>
+      <c r="Q86">
+        <v>40000</v>
+      </c>
+      <c r="R86">
+        <v>80000</v>
+      </c>
+      <c r="U86" s="41" t="s">
+        <v>99</v>
+      </c>
+      <c r="V86" s="40"/>
+      <c r="W86" s="40"/>
+      <c r="X86" s="40"/>
+      <c r="Y86" s="40"/>
+      <c r="Z86" s="40"/>
+      <c r="AA86" s="40"/>
+      <c r="AB86" s="40"/>
+      <c r="AC86" s="40"/>
+      <c r="AD86" s="40"/>
+      <c r="AE86" s="40"/>
+      <c r="AF86" s="40"/>
+    </row>
+    <row r="87" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="M87" t="str">
+        <v>Bakery</v>
+      </c>
+      <c r="N87" t="str">
+        <v>Breads</v>
+      </c>
+      <c r="O87">
+        <v>30000</v>
+      </c>
+      <c r="P87">
+        <v>15000</v>
+      </c>
+      <c r="Q87">
+        <v>20000</v>
+      </c>
+      <c r="R87">
+        <v>65000</v>
+      </c>
+    </row>
+    <row r="88" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A88" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="M88" t="str">
+        <v>Bakery</v>
+      </c>
+      <c r="N88" t="str">
+        <v>Desserts</v>
+      </c>
+      <c r="O88">
+        <v>25000</v>
+      </c>
+      <c r="P88">
+        <v>80000</v>
+      </c>
+      <c r="Q88">
+        <v>120000</v>
+      </c>
+      <c r="R88">
+        <v>225000</v>
+      </c>
+    </row>
+    <row r="89" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A89" t="str">
+        <f t="array" ref="A89:B94">TRANSPOSE(B78:G79)</f>
+        <v>Bread</v>
+      </c>
+      <c r="B89">
+        <v>50</v>
+      </c>
+      <c r="M89" t="str">
+        <v>Deli</v>
+      </c>
+      <c r="N89" t="str">
+        <v>Sandwiches</v>
+      </c>
+      <c r="O89">
+        <v>80000</v>
+      </c>
+      <c r="P89">
+        <v>40000</v>
+      </c>
+      <c r="Q89">
+        <v>20000</v>
+      </c>
+      <c r="R89">
+        <v>140000</v>
+      </c>
+    </row>
+    <row r="90" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A90" t="str">
+        <v>Donuts</v>
+      </c>
+      <c r="B90">
+        <v>100</v>
+      </c>
+      <c r="M90" t="str">
+        <v>Deli</v>
+      </c>
+      <c r="N90" t="str">
+        <v>Salads</v>
+      </c>
+      <c r="O90">
+        <v>90000</v>
+      </c>
+      <c r="P90">
+        <v>35000</v>
+      </c>
+      <c r="Q90">
+        <v>25000</v>
+      </c>
+      <c r="R90">
+        <v>150000</v>
+      </c>
+      <c r="V90" cm="1">
+        <f t="array" aca="1" ref="V90:Y95" ca="1">[1]!PivotTableData[#Data]</f>
+        <v>45982</v>
+      </c>
+      <c r="W90" t="str">
+        <f ca="1"/>
+        <v>Anne</v>
+      </c>
+      <c r="X90" t="str">
+        <f ca="1"/>
+        <v>Beer</v>
+      </c>
+      <c r="Y90">
+        <f ca="1"/>
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="91" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A91" t="str">
+        <v>Cookies</v>
+      </c>
+      <c r="B91">
+        <v>40</v>
+      </c>
+      <c r="M91" t="str">
+        <v>Meat</v>
+      </c>
+      <c r="N91" t="str">
+        <v>Beef</v>
+      </c>
+      <c r="O91">
+        <v>90000</v>
+      </c>
+      <c r="P91">
+        <v>110000</v>
+      </c>
+      <c r="Q91">
+        <v>200000</v>
+      </c>
+      <c r="R91">
+        <v>400000</v>
+      </c>
+      <c r="V91">
+        <f ca="1"/>
+        <v>45987</v>
+      </c>
+      <c r="W91" t="str">
+        <f ca="1"/>
+        <v>Mark</v>
+      </c>
+      <c r="X91" t="str">
+        <f ca="1"/>
+        <v>Wine</v>
+      </c>
+      <c r="Y91">
+        <f ca="1"/>
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="92" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A92" t="str">
+        <v>Cakes</v>
+      </c>
+      <c r="B92">
+        <v>50</v>
+      </c>
+      <c r="M92" t="str">
+        <v>Meat</v>
+      </c>
+      <c r="N92" t="str">
+        <v>Chicken</v>
+      </c>
+      <c r="O92">
+        <v>75000</v>
+      </c>
+      <c r="P92">
+        <v>82000</v>
+      </c>
+      <c r="Q92">
+        <v>150000</v>
+      </c>
+      <c r="R92">
+        <v>307000</v>
+      </c>
+      <c r="V92">
+        <f ca="1"/>
+        <v>46004</v>
+      </c>
+      <c r="W92" t="str">
+        <f ca="1"/>
+        <v>Anne</v>
+      </c>
+      <c r="X92" t="str">
+        <f ca="1"/>
+        <v>Beer</v>
+      </c>
+      <c r="Y92">
+        <f ca="1"/>
+        <v>750</v>
+      </c>
+    </row>
+    <row r="93" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A93" t="str">
+        <v>Pies</v>
+      </c>
+      <c r="B93">
+        <v>20</v>
+      </c>
+      <c r="V93">
+        <f ca="1"/>
+        <v>46008</v>
+      </c>
+      <c r="W93" t="str">
+        <f ca="1"/>
+        <v>Mark</v>
+      </c>
+      <c r="X93" t="str">
+        <f ca="1"/>
+        <v>Soda</v>
+      </c>
+      <c r="Y93">
+        <f ca="1"/>
+        <v>510</v>
+      </c>
+    </row>
+    <row r="94" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A94" t="str">
+        <v>butts</v>
+      </c>
+      <c r="B94">
+        <v>50</v>
+      </c>
+      <c r="M94" t="s">
+        <v>11</v>
+      </c>
+      <c r="N94" t="s">
+        <v>12</v>
+      </c>
+      <c r="O94" t="s">
+        <v>46</v>
+      </c>
+      <c r="V94">
+        <f ca="1"/>
+        <v>46028</v>
+      </c>
+      <c r="W94" t="str">
+        <f ca="1"/>
+        <v>Mariya</v>
+      </c>
+      <c r="X94" t="str">
+        <f ca="1"/>
+        <v>Soda</v>
+      </c>
+      <c r="Y94">
+        <f ca="1"/>
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="95" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="M95" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="M95" ca="1">[1]!TotalRows[#All]</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V95">
+        <f ca="1"/>
+        <v>46039</v>
+      </c>
+      <c r="W95" t="str">
+        <f ca="1"/>
+        <v>Laura</v>
+      </c>
+      <c r="X95" t="str">
+        <f ca="1"/>
+        <v>Wine</v>
+      </c>
+      <c r="Y95">
+        <f ca="1"/>
+        <v>680</v>
+      </c>
+    </row>
+    <row r="96" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="V96" s="36" t="s">
+        <v>100</v>
+      </c>
+      <c r="W96" t="s">
+        <v>105</v>
+      </c>
+      <c r="X96" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="97" spans="22:24" x14ac:dyDescent="0.3">
+      <c r="V97" s="42" t="s">
+        <v>101</v>
+      </c>
+      <c r="W97" s="37">
+        <v>750</v>
+      </c>
+      <c r="X97" s="37">
+        <v>46004</v>
+      </c>
+    </row>
+    <row r="98" spans="22:24" x14ac:dyDescent="0.3">
+      <c r="V98" s="42" t="s">
+        <v>102</v>
+      </c>
+      <c r="W98" s="37">
+        <v>2110</v>
+      </c>
+      <c r="X98" s="37">
+        <v>92036</v>
+      </c>
+    </row>
+    <row r="99" spans="22:24" x14ac:dyDescent="0.3">
+      <c r="V99" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="W99" s="37">
+        <v>1690</v>
+      </c>
+      <c r="X99" s="37">
+        <v>92026</v>
+      </c>
+    </row>
+    <row r="100" spans="22:24" x14ac:dyDescent="0.3">
+      <c r="V100" s="42" t="s">
+        <v>104</v>
+      </c>
+      <c r="W100" s="37">
+        <v>4550</v>
+      </c>
+      <c r="X100" s="37">
+        <v>230066</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="M36:P41" xr:uid="{D72B8E2B-2A1F-45B6-8C18-BFECD6D607E8}">
+    <filterColumn colId="2">
+      <customFilters>
+        <customFilter operator="greaterThan" val="25"/>
+      </customFilters>
+    </filterColumn>
+    <filterColumn colId="3">
+      <dynamicFilter type="belowAverage" val="3135.6"/>
+    </filterColumn>
+  </autoFilter>
+  <mergeCells count="17">
+    <mergeCell ref="U86:AF86"/>
+    <mergeCell ref="M49:Q49"/>
+    <mergeCell ref="U4:AG4"/>
+    <mergeCell ref="U27:AG27"/>
+    <mergeCell ref="V49:AG49"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="A25:H25"/>
+    <mergeCell ref="A27:K27"/>
+    <mergeCell ref="A49:K49"/>
+    <mergeCell ref="A71:G71"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="D4:H4"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="E6:H6"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="K4:R4"/>
+  </mergeCells>
+  <conditionalFormatting sqref="W32:Z41">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="dataBar" priority="2">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{4718937F-BFF2-4700-B40E-905EFC30677D}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X7:X18" xr:uid="{EBA881F1-A44D-451A-B1DD-44176FF8A316}">
+      <formula1>"Meat,Produce,Grain,Cereal, Bakery"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AB7:AB18" xr:uid="{58D8946F-6A6E-44E9-B6D6-AAA9B4883DD9}">
+      <formula1>"Produce,Meat,Bakery,Cereal"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AE7:AE18" xr:uid="{31423BC4-B72C-40B6-A970-013C8376668D}">
+      <formula1>$AC$21:$AC$26</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+  <tableParts count="4">
+    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId4"/>
+    <tablePart r:id="rId5"/>
+    <tablePart r:id="rId6"/>
+  </tableParts>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{4718937F-BFF2-4700-B40E-905EFC30677D}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>W32:Z41</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{05C60535-1F16-4fd2-B633-F4F36F0B64E0}">
+      <x14:sparklineGroups xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+        <x14:sparklineGroup displayEmptyCellsAs="span" xr2:uid="{04D15F5D-4451-48B9-B5F3-0345B9C83F93}">
+          <x14:colorSeries rgb="FF376092"/>
+          <x14:colorNegative rgb="FFD00000"/>
+          <x14:colorAxis rgb="FF000000"/>
+          <x14:colorMarkers rgb="FFD00000"/>
+          <x14:colorFirst rgb="FFD00000"/>
+          <x14:colorLast rgb="FFD00000"/>
+          <x14:colorHigh rgb="FFD00000"/>
+          <x14:colorLow rgb="FFD00000"/>
+          <x14:sparklines>
+            <x14:sparkline>
+              <xm:f>Hack!W32:Z32</xm:f>
+              <xm:sqref>AA32</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Hack!W33:Z33</xm:f>
+              <xm:sqref>AA33</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Hack!W34:Z34</xm:f>
+              <xm:sqref>AA34</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Hack!W35:Z35</xm:f>
+              <xm:sqref>AA35</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Hack!W36:Z36</xm:f>
+              <xm:sqref>AA36</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Hack!W37:Z37</xm:f>
+              <xm:sqref>AA37</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Hack!W38:Z38</xm:f>
+              <xm:sqref>AA38</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Hack!W39:Z39</xm:f>
+              <xm:sqref>AA39</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Hack!W40:Z40</xm:f>
+              <xm:sqref>AA40</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Hack!W41:Z41</xm:f>
+              <xm:sqref>AA41</xm:sqref>
+            </x14:sparkline>
+          </x14:sparklines>
+        </x14:sparklineGroup>
+      </x14:sparklineGroups>
+    </ext>
+  </extLst>
+</worksheet>
 </file>